--- a/data/trans_orig/IMC_inf_MED_R-Dificultad-trans_orig.xlsx
+++ b/data/trans_orig/IMC_inf_MED_R-Dificultad-trans_orig.xlsx
@@ -545,7 +545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la categoría de IMC recogido por medición en 2012 (tasa de respuesta: 70,03%)</t>
+          <t>Menores según la categoría de IMC recogido por medición en 2012 (tasa de respuesta: 83,37%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -735,19 +735,19 @@
         <v>40036</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>30995</v>
+        <v>31227</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>48961</v>
+        <v>49667</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.2303264352165113</v>
+        <v>0.1880491578188307</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.1783155353132376</v>
+        <v>0.1466722536847491</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.2816719422401433</v>
+        <v>0.2332897150708757</v>
       </c>
       <c r="J4" s="5" t="n">
         <v>31</v>
@@ -756,19 +756,19 @@
         <v>20778</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>14599</v>
+        <v>14919</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>27899</v>
+        <v>27928</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.1250144040616082</v>
+        <v>0.1036459252922531</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.08783924888070457</v>
+        <v>0.07441847209650661</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.1678624635802791</v>
+        <v>0.1393125901836589</v>
       </c>
       <c r="Q4" s="5" t="n">
         <v>87</v>
@@ -777,19 +777,19 @@
         <v>60814</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>50224</v>
+        <v>49659</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>72534</v>
+        <v>72868</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>0.1788501220980765</v>
+        <v>0.1471166072953965</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>0.1477070723182548</v>
+        <v>0.1201330886585082</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>0.2133190715767121</v>
+        <v>0.1762782437815536</v>
       </c>
     </row>
     <row r="5">
@@ -800,67 +800,67 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>24541</v>
+        <v>34220</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>17906</v>
+        <v>25848</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>33376</v>
+        <v>44419</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.1411835563990883</v>
+        <v>0.1607330386941587</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.1030113510011942</v>
+        <v>0.1214109666853036</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.1920115531074192</v>
+        <v>0.2086401594712088</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>21247</v>
+        <v>27301</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>14870</v>
+        <v>20122</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>29248</v>
+        <v>35586</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.1278352565604719</v>
+        <v>0.1361859824169203</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.08947006847622392</v>
+        <v>0.1003720540049208</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.1759759998393645</v>
+        <v>0.177511792232181</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>45787</v>
+        <v>61521</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>36161</v>
+        <v>51836</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>57056</v>
+        <v>75002</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.1346589337652253</v>
+        <v>0.1488285939093781</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>0.1063471953508463</v>
+        <v>0.1253996090758559</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>0.1678003711003843</v>
+        <v>0.1814413993983588</v>
       </c>
     </row>
     <row r="6">
@@ -871,67 +871,67 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>30782</v>
+        <v>40593</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>22484</v>
+        <v>31410</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>40062</v>
+        <v>51296</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.1770885236460598</v>
+        <v>0.1906691953709138</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.1293488493405001</v>
+        <v>0.1475328878354358</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.2304798296751436</v>
+        <v>0.2409374106887789</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>38855</v>
+        <v>49330</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>30453</v>
+        <v>39735</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>48968</v>
+        <v>59730</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.2337811951881991</v>
+        <v>0.2460692978643847</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.1832255391793187</v>
+        <v>0.1982099134547005</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.2946254183901087</v>
+        <v>0.2979514969906804</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>101</v>
+        <v>129</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>69637</v>
+        <v>89923</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>58248</v>
+        <v>76497</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>82663</v>
+        <v>105220</v>
       </c>
       <c r="U6" s="6" t="n">
-        <v>0.2047997896791987</v>
+        <v>0.2175362646339704</v>
       </c>
       <c r="V6" s="6" t="n">
-        <v>0.1713050103018018</v>
+        <v>0.1850562798020855</v>
       </c>
       <c r="W6" s="6" t="n">
-        <v>0.2431094410880389</v>
+        <v>0.2545407790767416</v>
       </c>
     </row>
     <row r="7">
@@ -942,67 +942,67 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>109</v>
+        <v>138</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>74948</v>
+        <v>94535</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>64709</v>
+        <v>82641</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>85583</v>
+        <v>106120</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.4311777371788514</v>
+        <v>0.4440370049519717</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.3722738873582572</v>
+        <v>0.3881676322251522</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.4923606807636968</v>
+        <v>0.498451034987711</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>114</v>
+        <v>139</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>78976</v>
+        <v>96714</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>68688</v>
+        <v>85792</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>89860</v>
+        <v>108232</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.4751770265839184</v>
+        <v>0.4824347842042824</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.4132750293947397</v>
+        <v>0.4279519155956157</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.5406597088702281</v>
+        <v>0.5398912183373259</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>223</v>
+        <v>277</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>153924</v>
+        <v>191249</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>139657</v>
+        <v>174968</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>169761</v>
+        <v>208649</v>
       </c>
       <c r="U7" s="6" t="n">
-        <v>0.4526845030589282</v>
+        <v>0.4626585552431643</v>
       </c>
       <c r="V7" s="6" t="n">
-        <v>0.4107270430076125</v>
+        <v>0.4232718393804608</v>
       </c>
       <c r="W7" s="6" t="n">
-        <v>0.4992618170274414</v>
+        <v>0.5047510579703991</v>
       </c>
     </row>
     <row r="8">
@@ -1019,19 +1019,19 @@
         <v>3515</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>1257</v>
+        <v>1273</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>7903</v>
+        <v>7454</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.02022374755948922</v>
+        <v>0.016511603164125</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.007229737369766115</v>
+        <v>0.005979698157889743</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.04546702257357353</v>
+        <v>0.03501238477337058</v>
       </c>
       <c r="J8" s="5" t="n">
         <v>10</v>
@@ -1040,19 +1040,19 @@
         <v>6348</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>3381</v>
+        <v>3188</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>11006</v>
+        <v>11595</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.03819211760580243</v>
+        <v>0.03166401022215952</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.02034126968552293</v>
+        <v>0.01590087768771501</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.06621870224838898</v>
+        <v>0.05783981313399333</v>
       </c>
       <c r="Q8" s="5" t="n">
         <v>15</v>
@@ -1061,19 +1061,19 @@
         <v>9863</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>5837</v>
+        <v>5616</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>15908</v>
+        <v>15764</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.02900665139857123</v>
+        <v>0.02385997891809078</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>0.01716640878064831</v>
+        <v>0.01358630304853176</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.04678458467741486</v>
+        <v>0.03813616152505484</v>
       </c>
     </row>
     <row r="9">
@@ -1084,16 +1084,16 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>251</v>
+        <v>304</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>173822</v>
+        <v>212900</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>173822</v>
+        <v>212900</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>173822</v>
+        <v>212900</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>1</v>
@@ -1105,16 +1105,16 @@
         <v>1</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>241</v>
+        <v>290</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>166204</v>
+        <v>200470</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>166204</v>
+        <v>200470</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>166204</v>
+        <v>200470</v>
       </c>
       <c r="N9" s="6" t="n">
         <v>1</v>
@@ -1126,16 +1126,16 @@
         <v>1</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>492</v>
+        <v>594</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>340025</v>
+        <v>413370</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>340025</v>
+        <v>413370</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>340025</v>
+        <v>413370</v>
       </c>
       <c r="U9" s="6" t="n">
         <v>1</v>
@@ -1165,19 +1165,19 @@
         <v>20805</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>13942</v>
+        <v>13472</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>28588</v>
+        <v>28133</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.1283169448209316</v>
+        <v>0.1140239042092067</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.08598567289626639</v>
+        <v>0.07383408492927281</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.1763161235127074</v>
+        <v>0.154181938784652</v>
       </c>
       <c r="J10" s="5" t="n">
         <v>22</v>
@@ -1186,19 +1186,19 @@
         <v>15244</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>10483</v>
+        <v>9779</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>23002</v>
+        <v>22421</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.09915148011822679</v>
+        <v>0.08494886164017712</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.06818284194705405</v>
+        <v>0.05449057156970176</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.1496061780865838</v>
+        <v>0.1249367989247567</v>
       </c>
       <c r="Q10" s="5" t="n">
         <v>50</v>
@@ -1207,19 +1207,19 @@
         <v>36050</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>26874</v>
+        <v>27230</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>45655</v>
+        <v>45879</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.1141215311331016</v>
+        <v>0.09960724916640035</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.08507403932413321</v>
+        <v>0.07523804403425256</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.1445284853032836</v>
+        <v>0.1267659289526228</v>
       </c>
     </row>
     <row r="11">
@@ -1230,67 +1230,67 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>19394</v>
+        <v>21414</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>13391</v>
+        <v>14747</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>27253</v>
+        <v>29220</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.1196142409565048</v>
+        <v>0.1173626577247086</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.08258797305436641</v>
+        <v>0.0808238637970434</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.1680848930625862</v>
+        <v>0.1601428928193498</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>19929</v>
+        <v>24382</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>13229</v>
+        <v>17547</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>28352</v>
+        <v>32963</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.1296210451771442</v>
+        <v>0.1358652445615496</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.08604275614215587</v>
+        <v>0.0977806703464212</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.1844063736773039</v>
+        <v>0.1836840905546295</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="R11" s="5" t="n">
-        <v>39323</v>
+        <v>45796</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>30589</v>
+        <v>35976</v>
       </c>
       <c r="T11" s="5" t="n">
-        <v>49599</v>
+        <v>56844</v>
       </c>
       <c r="U11" s="6" t="n">
-        <v>0.1244847522633905</v>
+        <v>0.1265370350688862</v>
       </c>
       <c r="V11" s="6" t="n">
-        <v>0.09683432363313406</v>
+        <v>0.09940250440427006</v>
       </c>
       <c r="W11" s="6" t="n">
-        <v>0.1570137770745408</v>
+        <v>0.1570633252566108</v>
       </c>
     </row>
     <row r="12">
@@ -1301,67 +1301,67 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>53836</v>
+        <v>58059</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>44268</v>
+        <v>47862</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>63771</v>
+        <v>68275</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.3320339641123936</v>
+        <v>0.318194213213516</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.2730239135945017</v>
+        <v>0.2623111160571997</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.3933081325007898</v>
+        <v>0.3741829454576212</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>32941</v>
+        <v>37873</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>25085</v>
+        <v>29135</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>41277</v>
+        <v>47245</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.214253230676123</v>
+        <v>0.2110462736089918</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.1631527790688733</v>
+        <v>0.1623539521278833</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.2684669471855964</v>
+        <v>0.2632686861260413</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>86777</v>
+        <v>95932</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>74519</v>
+        <v>82398</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>100392</v>
+        <v>110694</v>
       </c>
       <c r="U12" s="6" t="n">
-        <v>0.2747077307529494</v>
+        <v>0.2650656621491991</v>
       </c>
       <c r="V12" s="6" t="n">
-        <v>0.2359030633840606</v>
+        <v>0.2276714661378098</v>
       </c>
       <c r="W12" s="6" t="n">
-        <v>0.3178088261182401</v>
+        <v>0.3058534819817527</v>
       </c>
     </row>
     <row r="13">
@@ -1372,67 +1372,67 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>60792</v>
+        <v>74873</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>50809</v>
+        <v>63833</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>70436</v>
+        <v>85747</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.3749351588404047</v>
+        <v>0.4103431235677003</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.3133651314327033</v>
+        <v>0.3498382578472731</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.434414774004144</v>
+        <v>0.4699402532928914</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>116</v>
+        <v>140</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>80480</v>
+        <v>96802</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>70534</v>
+        <v>86855</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>90976</v>
+        <v>106751</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.5234535872766706</v>
+        <v>0.5394205165601258</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.4587575894418996</v>
+        <v>0.483992900953518</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.5917149739885986</v>
+        <v>0.5948618396900254</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>201</v>
+        <v>245</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>141273</v>
+        <v>171674</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>126268</v>
+        <v>155359</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>156825</v>
+        <v>186501</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.4472220417483134</v>
+        <v>0.4743452396154588</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.3997215724358393</v>
+        <v>0.4292668953532714</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.4964555169732696</v>
+        <v>0.5153115293731383</v>
       </c>
     </row>
     <row r="14">
@@ -1449,19 +1449,19 @@
         <v>7312</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>3718</v>
+        <v>3629</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>13324</v>
+        <v>12985</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.04509969126976529</v>
+        <v>0.04007610128486834</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.02293276954285632</v>
+        <v>0.01988625415230003</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.08217661229930293</v>
+        <v>0.07116552224402749</v>
       </c>
       <c r="J14" s="5" t="n">
         <v>8</v>
@@ -1470,19 +1470,19 @@
         <v>5154</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>2079</v>
+        <v>2186</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>9471</v>
+        <v>9132</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.0335206567518354</v>
+        <v>0.02871910362915579</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.01352451176896202</v>
+        <v>0.0121821902001297</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.06159947755115423</v>
+        <v>0.05088569965130417</v>
       </c>
       <c r="Q14" s="5" t="n">
         <v>18</v>
@@ -1491,19 +1491,19 @@
         <v>12466</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>8185</v>
+        <v>7475</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>19079</v>
+        <v>19251</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.03946394410224514</v>
+        <v>0.03444481400005549</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.02591201606551272</v>
+        <v>0.02065423639886814</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.06039823003761851</v>
+        <v>0.05319127429160622</v>
       </c>
     </row>
     <row r="15">
@@ -1514,16 +1514,16 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>230</v>
+        <v>260</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>162139</v>
+        <v>182464</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>162139</v>
+        <v>182464</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>162139</v>
+        <v>182464</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>1</v>
@@ -1535,16 +1535,16 @@
         <v>1</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>220</v>
+        <v>257</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>153749</v>
+        <v>179455</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>153749</v>
+        <v>179455</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>153749</v>
+        <v>179455</v>
       </c>
       <c r="N15" s="6" t="n">
         <v>1</v>
@@ -1556,16 +1556,16 @@
         <v>1</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>450</v>
+        <v>517</v>
       </c>
       <c r="R15" s="5" t="n">
-        <v>315889</v>
+        <v>361918</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>315889</v>
+        <v>361918</v>
       </c>
       <c r="T15" s="5" t="n">
-        <v>315889</v>
+        <v>361918</v>
       </c>
       <c r="U15" s="6" t="n">
         <v>1</v>
@@ -1595,19 +1595,19 @@
         <v>11586</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>7106</v>
+        <v>7256</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>17943</v>
+        <v>17721</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.1084646530529812</v>
+        <v>0.08554264849627134</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.06652899683227963</v>
+        <v>0.05357318087447712</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.1679809568714233</v>
+        <v>0.1308407288433694</v>
       </c>
       <c r="J16" s="5" t="n">
         <v>14</v>
@@ -1616,19 +1616,19 @@
         <v>9520</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>5517</v>
+        <v>5350</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>15498</v>
+        <v>15466</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.08844461474630312</v>
+        <v>0.07182735742486497</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.0512523930562494</v>
+        <v>0.04036963678321024</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.1439911700673875</v>
+        <v>0.1166970201783127</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>31</v>
@@ -1637,19 +1637,19 @@
         <v>21105</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>14305</v>
+        <v>14881</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>28552</v>
+        <v>29219</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>0.09841642023062346</v>
+        <v>0.0787592788083693</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>0.06670451644416643</v>
+        <v>0.05553268382477624</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>0.13314021270916</v>
+        <v>0.1090379509047385</v>
       </c>
     </row>
     <row r="17">
@@ -1660,67 +1660,67 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>7610</v>
+        <v>8261</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>3981</v>
+        <v>4264</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>13398</v>
+        <v>14287</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.07124293089648671</v>
+        <v>0.06099556054279848</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.03726594564570435</v>
+        <v>0.03148397884730223</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.1254345586048383</v>
+        <v>0.1054914382690859</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>9332</v>
+        <v>11977</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>5408</v>
+        <v>7193</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>15376</v>
+        <v>17608</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.08669976386298775</v>
+        <v>0.09036772888309878</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.05024323955620035</v>
+        <v>0.05427504905603307</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.1428546068504378</v>
+        <v>0.132855091746484</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>16942</v>
+        <v>20238</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>10947</v>
+        <v>13540</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>23625</v>
+        <v>28003</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>0.07900085093462614</v>
+        <v>0.07552257825975595</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>0.05104833046764903</v>
+        <v>0.05052778690397474</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>0.1101663461940695</v>
+        <v>0.104499199068063</v>
       </c>
     </row>
     <row r="18">
@@ -1731,67 +1731,67 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>32719</v>
+        <v>42662</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>25176</v>
+        <v>34929</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>41035</v>
+        <v>51501</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.3063104246788088</v>
+        <v>0.3149933936177345</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.2356998446451687</v>
+        <v>0.2578985428195335</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0.3841732834038007</v>
+        <v>0.3802570395548153</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>22256</v>
+        <v>30172</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>15950</v>
+        <v>21880</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>31047</v>
+        <v>38567</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.2067770690269724</v>
+        <v>0.2276536014243295</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.1481908578903262</v>
+        <v>0.1650855036234381</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.2884507599944007</v>
+        <v>0.2909929168169904</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="R18" s="5" t="n">
-        <v>54975</v>
+        <v>72834</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>44588</v>
+        <v>61238</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>65333</v>
+        <v>84562</v>
       </c>
       <c r="U18" s="6" t="n">
-        <v>0.2563537604677032</v>
+        <v>0.2717964905532737</v>
       </c>
       <c r="V18" s="6" t="n">
-        <v>0.2079203624566774</v>
+        <v>0.2285227880819123</v>
       </c>
       <c r="W18" s="6" t="n">
-        <v>0.3046562165396681</v>
+        <v>0.3155636892311147</v>
       </c>
     </row>
     <row r="19">
@@ -1802,67 +1802,67 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>52912</v>
+        <v>70939</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>44477</v>
+        <v>61736</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>61251</v>
+        <v>79865</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.4953572447558923</v>
+        <v>0.5237796475224413</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>0.4163974506231651</v>
+        <v>0.4558289148608907</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.573433884233446</v>
+        <v>0.5896845309631129</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>61819</v>
+        <v>76160</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>53391</v>
+        <v>67405</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>70440</v>
+        <v>85800</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.5743491081222006</v>
+        <v>0.5746378959841132</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.4960426692727115</v>
+        <v>0.5085848965886344</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.6544404084470358</v>
+        <v>0.6473751551713927</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>166</v>
+        <v>212</v>
       </c>
       <c r="R19" s="5" t="n">
-        <v>114731</v>
+        <v>147099</v>
       </c>
       <c r="S19" s="5" t="n">
-        <v>102407</v>
+        <v>133966</v>
       </c>
       <c r="T19" s="5" t="n">
-        <v>126083</v>
+        <v>161087</v>
       </c>
       <c r="U19" s="6" t="n">
-        <v>0.53500395381897</v>
+        <v>0.5489333463538085</v>
       </c>
       <c r="V19" s="6" t="n">
-        <v>0.4775360155348852</v>
+        <v>0.4999253662145445</v>
       </c>
       <c r="W19" s="6" t="n">
-        <v>0.5879408769247562</v>
+        <v>0.6011331890361618</v>
       </c>
     </row>
     <row r="20">
@@ -1882,16 +1882,16 @@
         <v>605</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>5295</v>
+        <v>5491</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.01862474661583106</v>
+        <v>0.01468874982075431</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.005664389764595861</v>
+        <v>0.004469624714739552</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.04957089405674017</v>
+        <v>0.04054641938789921</v>
       </c>
       <c r="J20" s="5" t="n">
         <v>7</v>
@@ -1900,19 +1900,19 @@
         <v>4707</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>2002</v>
+        <v>2009</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>9125</v>
+        <v>8955</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.0437294442415361</v>
+        <v>0.03551341628359352</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.01859550874731131</v>
+        <v>0.01515682208342278</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.08477529236263741</v>
+        <v>0.06756439574549034</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>10</v>
@@ -1921,19 +1921,19 @@
         <v>6696</v>
       </c>
       <c r="S20" s="5" t="n">
-        <v>3193</v>
+        <v>3341</v>
       </c>
       <c r="T20" s="5" t="n">
-        <v>11468</v>
+        <v>12025</v>
       </c>
       <c r="U20" s="6" t="n">
-        <v>0.03122501454807722</v>
+        <v>0.02498830602479253</v>
       </c>
       <c r="V20" s="6" t="n">
-        <v>0.01488966607688082</v>
+        <v>0.01246728996768608</v>
       </c>
       <c r="W20" s="6" t="n">
-        <v>0.05347693067758038</v>
+        <v>0.04487452731242057</v>
       </c>
     </row>
     <row r="21">
@@ -1944,16 +1944,16 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>156</v>
+        <v>197</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>106815</v>
+        <v>135437</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>106815</v>
+        <v>135437</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>106815</v>
+        <v>135437</v>
       </c>
       <c r="G21" s="6" t="n">
         <v>1</v>
@@ -1965,16 +1965,16 @@
         <v>1</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>154</v>
+        <v>190</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>107634</v>
+        <v>132535</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>107634</v>
+        <v>132535</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>107634</v>
+        <v>132535</v>
       </c>
       <c r="N21" s="6" t="n">
         <v>1</v>
@@ -1986,16 +1986,16 @@
         <v>1</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>310</v>
+        <v>387</v>
       </c>
       <c r="R21" s="5" t="n">
-        <v>214449</v>
+        <v>267972</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>214449</v>
+        <v>267972</v>
       </c>
       <c r="T21" s="5" t="n">
-        <v>214449</v>
+        <v>267972</v>
       </c>
       <c r="U21" s="6" t="n">
         <v>1</v>
@@ -2025,19 +2025,19 @@
         <v>9089</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>5041</v>
+        <v>5313</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>14909</v>
+        <v>15092</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.1402920663930884</v>
+        <v>0.1184277998542718</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.0778176958004702</v>
+        <v>0.06922554535138774</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.2301345136772063</v>
+        <v>0.1966514703522646</v>
       </c>
       <c r="J22" s="5" t="n">
         <v>9</v>
@@ -2046,19 +2046,19 @@
         <v>6218</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>2944</v>
+        <v>2777</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>11155</v>
+        <v>10724</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.1045395913714603</v>
+        <v>0.09257798279447073</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.04949935815634936</v>
+        <v>0.04134792420545952</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.1875378934501764</v>
+        <v>0.1596648431359002</v>
       </c>
       <c r="Q22" s="5" t="n">
         <v>21</v>
@@ -2067,19 +2067,19 @@
         <v>15307</v>
       </c>
       <c r="S22" s="5" t="n">
-        <v>9786</v>
+        <v>10059</v>
       </c>
       <c r="T22" s="5" t="n">
-        <v>22667</v>
+        <v>22624</v>
       </c>
       <c r="U22" s="6" t="n">
-        <v>0.123178800672067</v>
+        <v>0.106363203949566</v>
       </c>
       <c r="V22" s="6" t="n">
-        <v>0.07874534427622822</v>
+        <v>0.0698932158752097</v>
       </c>
       <c r="W22" s="6" t="n">
-        <v>0.1824015849637633</v>
+        <v>0.1572063403121903</v>
       </c>
     </row>
     <row r="23">
@@ -2090,67 +2090,67 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>8429</v>
+        <v>10982</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>4671</v>
+        <v>6716</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>13913</v>
+        <v>17322</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.1301107707069602</v>
+        <v>0.1430921519732085</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.07209219001291242</v>
+        <v>0.08750968220201567</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.2147474258448934</v>
+        <v>0.2257017157125218</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>4393</v>
+        <v>7370</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>1983</v>
+        <v>3927</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>8312</v>
+        <v>12988</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.07386013293327456</v>
+        <v>0.1097307676796764</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.03333429370794179</v>
+        <v>0.05846343905851595</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.1397419866559423</v>
+        <v>0.1933593572471386</v>
       </c>
       <c r="Q23" s="5" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="R23" s="5" t="n">
-        <v>12823</v>
+        <v>18352</v>
       </c>
       <c r="S23" s="5" t="n">
-        <v>7936</v>
+        <v>12549</v>
       </c>
       <c r="T23" s="5" t="n">
-        <v>18724</v>
+        <v>26006</v>
       </c>
       <c r="U23" s="6" t="n">
-        <v>0.1031858624141589</v>
+        <v>0.1275217663340399</v>
       </c>
       <c r="V23" s="6" t="n">
-        <v>0.0638618696023753</v>
+        <v>0.08719964079667891</v>
       </c>
       <c r="W23" s="6" t="n">
-        <v>0.1506744490741126</v>
+        <v>0.1807034061895964</v>
       </c>
     </row>
     <row r="24">
@@ -2161,67 +2161,67 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>12021</v>
+        <v>16592</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>7824</v>
+        <v>11297</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>18145</v>
+        <v>22904</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>0.1855528518530431</v>
+        <v>0.2161844586236615</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>0.1207638947844412</v>
+        <v>0.1471997941174721</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>0.2800686514866357</v>
+        <v>0.2984299571912706</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>18160</v>
+        <v>19612</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>12987</v>
+        <v>13209</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>24801</v>
+        <v>25807</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>0.3053066872409171</v>
+        <v>0.291988355231908</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.2183368347242821</v>
+        <v>0.1966606701561623</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.4169543719552637</v>
+        <v>0.3842192878711989</v>
       </c>
       <c r="Q24" s="5" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="R24" s="5" t="n">
-        <v>30182</v>
+        <v>36204</v>
       </c>
       <c r="S24" s="5" t="n">
-        <v>22780</v>
+        <v>27778</v>
       </c>
       <c r="T24" s="5" t="n">
-        <v>38413</v>
+        <v>46176</v>
       </c>
       <c r="U24" s="6" t="n">
-        <v>0.2428741758974454</v>
+        <v>0.2515635631823081</v>
       </c>
       <c r="V24" s="6" t="n">
-        <v>0.1833095314127147</v>
+        <v>0.1930165363195565</v>
       </c>
       <c r="W24" s="6" t="n">
-        <v>0.3091079563709717</v>
+        <v>0.3208575965388191</v>
       </c>
     </row>
     <row r="25">
@@ -2232,67 +2232,67 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>31027</v>
+        <v>35865</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>24353</v>
+        <v>28113</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>38155</v>
+        <v>43153</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0.4789080588106191</v>
+        <v>0.4673107052184593</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.3758992925773304</v>
+        <v>0.366312312458521</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.5889359964597711</v>
+        <v>0.5622695705053117</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>29368</v>
+        <v>32625</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>23348</v>
+        <v>25881</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>36096</v>
+        <v>39284</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.4937300388516748</v>
+        <v>0.4857211067291167</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.3925254957814328</v>
+        <v>0.3853148083309531</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.6068410864666381</v>
+        <v>0.5848602015046788</v>
       </c>
       <c r="Q25" s="5" t="n">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="R25" s="5" t="n">
-        <v>60395</v>
+        <v>68490</v>
       </c>
       <c r="S25" s="5" t="n">
-        <v>51121</v>
+        <v>58308</v>
       </c>
       <c r="T25" s="5" t="n">
-        <v>70032</v>
+        <v>78730</v>
       </c>
       <c r="U25" s="6" t="n">
-        <v>0.4860027419843244</v>
+        <v>0.4759031859372059</v>
       </c>
       <c r="V25" s="6" t="n">
-        <v>0.4113708085773242</v>
+        <v>0.4051573121482808</v>
       </c>
       <c r="W25" s="6" t="n">
-        <v>0.5635484492345366</v>
+        <v>0.5470568974021658</v>
       </c>
     </row>
     <row r="26">
@@ -2309,19 +2309,19 @@
         <v>4220</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>1392</v>
+        <v>1626</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>9031</v>
+        <v>8768</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.06513625223628915</v>
+        <v>0.05498488433039894</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.02148418799247381</v>
+        <v>0.02118587616386585</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.1393949590995421</v>
+        <v>0.114244879009048</v>
       </c>
       <c r="J26" s="5" t="n">
         <v>2</v>
@@ -2333,16 +2333,16 @@
         <v>0</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>4610</v>
+        <v>4672</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.02256354960267319</v>
+        <v>0.01998178756482818</v>
       </c>
       <c r="O26" s="6" t="n">
         <v>0</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.07750501171237922</v>
+        <v>0.06956075949426575</v>
       </c>
       <c r="Q26" s="5" t="n">
         <v>8</v>
@@ -2351,19 +2351,19 @@
         <v>5562</v>
       </c>
       <c r="S26" s="5" t="n">
-        <v>2665</v>
+        <v>2615</v>
       </c>
       <c r="T26" s="5" t="n">
-        <v>10177</v>
+        <v>10182</v>
       </c>
       <c r="U26" s="6" t="n">
-        <v>0.04475841903200432</v>
+        <v>0.03864828059688013</v>
       </c>
       <c r="V26" s="6" t="n">
-        <v>0.02144757112972418</v>
+        <v>0.01816779040328102</v>
       </c>
       <c r="W26" s="6" t="n">
-        <v>0.08189516019135087</v>
+        <v>0.07074862293651203</v>
       </c>
     </row>
     <row r="27">
@@ -2374,16 +2374,16 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>64786</v>
+        <v>76747</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>64786</v>
+        <v>76747</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>64786</v>
+        <v>76747</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>1</v>
@@ -2395,16 +2395,16 @@
         <v>1</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>59482</v>
+        <v>67168</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>59482</v>
+        <v>67168</v>
       </c>
       <c r="M27" s="5" t="n">
-        <v>59482</v>
+        <v>67168</v>
       </c>
       <c r="N27" s="6" t="n">
         <v>1</v>
@@ -2416,16 +2416,16 @@
         <v>1</v>
       </c>
       <c r="Q27" s="5" t="n">
-        <v>175</v>
+        <v>201</v>
       </c>
       <c r="R27" s="5" t="n">
-        <v>124269</v>
+        <v>143915</v>
       </c>
       <c r="S27" s="5" t="n">
-        <v>124269</v>
+        <v>143915</v>
       </c>
       <c r="T27" s="5" t="n">
-        <v>124269</v>
+        <v>143915</v>
       </c>
       <c r="U27" s="6" t="n">
         <v>1</v>
@@ -2455,19 +2455,19 @@
         <v>81516</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>70213</v>
+        <v>67825</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>96985</v>
+        <v>95873</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0.1606021598827287</v>
+        <v>0.1341713735394592</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>0.1383344123447331</v>
+        <v>0.1116369841357464</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>0.1910794447118614</v>
+        <v>0.1578039893351417</v>
       </c>
       <c r="J28" s="5" t="n">
         <v>76</v>
@@ -2476,19 +2476,19 @@
         <v>51760</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>41151</v>
+        <v>40921</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>63228</v>
+        <v>63674</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.1062687289494745</v>
+        <v>0.08929919227930459</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.08448669751152869</v>
+        <v>0.07059861024371496</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.1298131622176709</v>
+        <v>0.1098542369525049</v>
       </c>
       <c r="Q28" s="5" t="n">
         <v>189</v>
@@ -2497,19 +2497,19 @@
         <v>133276</v>
       </c>
       <c r="S28" s="5" t="n">
-        <v>115344</v>
+        <v>114378</v>
       </c>
       <c r="T28" s="5" t="n">
-        <v>151466</v>
+        <v>151311</v>
       </c>
       <c r="U28" s="6" t="n">
-        <v>0.13399518101487</v>
+        <v>0.1122629620740379</v>
       </c>
       <c r="V28" s="6" t="n">
-        <v>0.1159661369056802</v>
+        <v>0.09634448354915369</v>
       </c>
       <c r="W28" s="6" t="n">
-        <v>0.1522837764174841</v>
+        <v>0.1274546382404621</v>
       </c>
     </row>
     <row r="29">
@@ -2520,67 +2520,67 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>59974</v>
+        <v>74877</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>48982</v>
+        <v>62730</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>73183</v>
+        <v>89100</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0.1181611355909653</v>
+        <v>0.1232453607345691</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>0.09650441982379558</v>
+        <v>0.10325154898032</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>0.1441862972004545</v>
+        <v>0.1466558150659368</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>54901</v>
+        <v>71030</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>44935</v>
+        <v>58729</v>
       </c>
       <c r="M29" s="5" t="n">
-        <v>68384</v>
+        <v>84454</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.1127171327082831</v>
+        <v>0.12254442968068</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.09225515167453675</v>
+        <v>0.1013212167099348</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.1403996660783398</v>
+        <v>0.1457034388337452</v>
       </c>
       <c r="Q29" s="5" t="n">
-        <v>165</v>
+        <v>205</v>
       </c>
       <c r="R29" s="5" t="n">
-        <v>114875</v>
+        <v>145908</v>
       </c>
       <c r="S29" s="5" t="n">
-        <v>99484</v>
+        <v>129190</v>
       </c>
       <c r="T29" s="5" t="n">
-        <v>131792</v>
+        <v>166576</v>
       </c>
       <c r="U29" s="6" t="n">
-        <v>0.115495217625394</v>
+        <v>0.1229031378805371</v>
       </c>
       <c r="V29" s="6" t="n">
-        <v>0.1000207974778577</v>
+        <v>0.1088211428310255</v>
       </c>
       <c r="W29" s="6" t="n">
-        <v>0.1325029765615401</v>
+        <v>0.140312612531795</v>
       </c>
     </row>
     <row r="30">
@@ -2591,67 +2591,67 @@
         </is>
       </c>
       <c r="C30" s="5" t="n">
-        <v>188</v>
+        <v>227</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>129357</v>
+        <v>157906</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>112855</v>
+        <v>140191</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>145587</v>
+        <v>175610</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.2548601938652048</v>
+        <v>0.2599065382678674</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>0.2223480509544812</v>
+        <v>0.2307480998339095</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>0.2868368684199558</v>
+        <v>0.2890473989708496</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>158</v>
+        <v>195</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>112213</v>
+        <v>136987</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>98271</v>
+        <v>122387</v>
       </c>
       <c r="M30" s="5" t="n">
-        <v>128366</v>
+        <v>156187</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.2303844252712953</v>
+        <v>0.2363363428369359</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.2017608704929549</v>
+        <v>0.2111481680156984</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.2635488068395861</v>
+        <v>0.269461791821729</v>
       </c>
       <c r="Q30" s="5" t="n">
-        <v>346</v>
+        <v>422</v>
       </c>
       <c r="R30" s="5" t="n">
-        <v>241570</v>
+        <v>294893</v>
       </c>
       <c r="S30" s="5" t="n">
-        <v>219546</v>
+        <v>270959</v>
       </c>
       <c r="T30" s="5" t="n">
-        <v>263907</v>
+        <v>319774</v>
       </c>
       <c r="U30" s="6" t="n">
-        <v>0.2428744560502535</v>
+        <v>0.2483986167601653</v>
       </c>
       <c r="V30" s="6" t="n">
-        <v>0.2207308350055658</v>
+        <v>0.2282385173981898</v>
       </c>
       <c r="W30" s="6" t="n">
-        <v>0.2653318020236195</v>
+        <v>0.2693567238693965</v>
       </c>
     </row>
     <row r="31">
@@ -2662,67 +2662,67 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>317</v>
+        <v>399</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>219678</v>
+        <v>276212</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>199756</v>
+        <v>256934</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>238721</v>
+        <v>296811</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.4328100019325523</v>
+        <v>0.4546343612513096</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0.3935596412439525</v>
+        <v>0.4229034785416099</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>0.4703288516299558</v>
+        <v>0.4885383770582932</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>359</v>
+        <v>433</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>250644</v>
+        <v>302299</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>232975</v>
+        <v>283492</v>
       </c>
       <c r="M31" s="5" t="n">
-        <v>269076</v>
+        <v>323503</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.5145971539724734</v>
+        <v>0.5215413402844656</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.4783205125718249</v>
+        <v>0.489093560263354</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.5524391335325418</v>
+        <v>0.5581225284447182</v>
       </c>
       <c r="Q31" s="5" t="n">
-        <v>676</v>
+        <v>832</v>
       </c>
       <c r="R31" s="5" t="n">
-        <v>470322</v>
+        <v>578512</v>
       </c>
       <c r="S31" s="5" t="n">
-        <v>446836</v>
+        <v>548862</v>
       </c>
       <c r="T31" s="5" t="n">
-        <v>495277</v>
+        <v>605259</v>
       </c>
       <c r="U31" s="6" t="n">
-        <v>0.4728610163560988</v>
+        <v>0.487301051066728</v>
       </c>
       <c r="V31" s="6" t="n">
-        <v>0.4492479403566214</v>
+        <v>0.4623262164635369</v>
       </c>
       <c r="W31" s="6" t="n">
-        <v>0.4979506055054216</v>
+        <v>0.509831434602856</v>
       </c>
     </row>
     <row r="32">
@@ -2739,19 +2739,19 @@
         <v>17037</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>11048</v>
+        <v>11043</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>25036</v>
+        <v>25352</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>0.03356650872854897</v>
+        <v>0.02804236620679464</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>0.02176683554709359</v>
+        <v>0.01817601182158504</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>0.04932592138086072</v>
+        <v>0.04172759229147868</v>
       </c>
       <c r="J32" s="5" t="n">
         <v>27</v>
@@ -2760,19 +2760,19 @@
         <v>17550</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>11854</v>
+        <v>11825</v>
       </c>
       <c r="M32" s="5" t="n">
-        <v>24615</v>
+        <v>26196</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.03603255909847368</v>
+        <v>0.03027869491861386</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.02433817404395105</v>
+        <v>0.02040163128143307</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.05053777040483216</v>
+        <v>0.04519456505633899</v>
       </c>
       <c r="Q32" s="5" t="n">
         <v>51</v>
@@ -2781,19 +2781,19 @@
         <v>34587</v>
       </c>
       <c r="S32" s="5" t="n">
-        <v>26902</v>
+        <v>26121</v>
       </c>
       <c r="T32" s="5" t="n">
-        <v>44575</v>
+        <v>45892</v>
       </c>
       <c r="U32" s="6" t="n">
-        <v>0.03477412895338376</v>
+        <v>0.02913423221853178</v>
       </c>
       <c r="V32" s="6" t="n">
-        <v>0.02704725226516832</v>
+        <v>0.0220029590140823</v>
       </c>
       <c r="W32" s="6" t="n">
-        <v>0.04481592514157755</v>
+        <v>0.03865659035324937</v>
       </c>
     </row>
     <row r="33">
@@ -2804,16 +2804,16 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>729</v>
+        <v>869</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>507562</v>
+        <v>607548</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>507562</v>
+        <v>607548</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>507562</v>
+        <v>607548</v>
       </c>
       <c r="G33" s="6" t="n">
         <v>1</v>
@@ -2825,16 +2825,16 @@
         <v>1</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>698</v>
+        <v>830</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>487069</v>
+        <v>579627</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>487069</v>
+        <v>579627</v>
       </c>
       <c r="M33" s="5" t="n">
-        <v>487069</v>
+        <v>579627</v>
       </c>
       <c r="N33" s="6" t="n">
         <v>1</v>
@@ -2846,16 +2846,16 @@
         <v>1</v>
       </c>
       <c r="Q33" s="5" t="n">
-        <v>1427</v>
+        <v>1699</v>
       </c>
       <c r="R33" s="5" t="n">
-        <v>994631</v>
+        <v>1187175</v>
       </c>
       <c r="S33" s="5" t="n">
-        <v>994631</v>
+        <v>1187175</v>
       </c>
       <c r="T33" s="5" t="n">
-        <v>994631</v>
+        <v>1187175</v>
       </c>
       <c r="U33" s="6" t="n">
         <v>1</v>
@@ -2927,7 +2927,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la categoría de IMC recogido por medición en 2016 (tasa de respuesta: 69,19%)</t>
+          <t>Menores según la categoría de IMC recogido por medición en 2016 (tasa de respuesta: 82,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3117,19 +3117,19 @@
         <v>19651</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>12915</v>
+        <v>13254</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>26731</v>
+        <v>28403</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.0989395643457283</v>
+        <v>0.07977369156285001</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.06502499047374471</v>
+        <v>0.05380427168470762</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.1345852507371496</v>
+        <v>0.1153008413260376</v>
       </c>
       <c r="J4" s="5" t="n">
         <v>18</v>
@@ -3138,19 +3138,19 @@
         <v>11349</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>6872</v>
+        <v>7355</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>16856</v>
+        <v>17783</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.0637274756762022</v>
+        <v>0.05230189832561866</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.03858853728609882</v>
+        <v>0.0338979734097017</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.09465206460662332</v>
+        <v>0.08195598190352095</v>
       </c>
       <c r="Q4" s="5" t="n">
         <v>45</v>
@@ -3159,19 +3159,19 @@
         <v>31000</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>23411</v>
+        <v>23062</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>40873</v>
+        <v>40755</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>0.08229343393632313</v>
+        <v>0.06690806195394788</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>0.06214919093698172</v>
+        <v>0.04977636506851811</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>0.1085043509804391</v>
+        <v>0.08796255374376401</v>
       </c>
     </row>
     <row r="5">
@@ -3182,67 +3182,67 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>25306</v>
+        <v>34620</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>18499</v>
+        <v>26096</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>33572</v>
+        <v>44512</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.1274086987807177</v>
+        <v>0.1405394271195081</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.09314126356722675</v>
+        <v>0.1059381146362047</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.1690294191746633</v>
+        <v>0.1806969160270522</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>15923</v>
+        <v>17893</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>10723</v>
+        <v>12203</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>23115</v>
+        <v>25289</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.08941496513285253</v>
+        <v>0.08246560431176124</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.06021655421646025</v>
+        <v>0.05624149892243233</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.129799828586956</v>
+        <v>0.1165501809614299</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>41228</v>
+        <v>52513</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>32546</v>
+        <v>42648</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>53274</v>
+        <v>64853</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.1094475760828212</v>
+        <v>0.1133422111327157</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>0.08639877983734098</v>
+        <v>0.0920491772149731</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>0.141424899286976</v>
+        <v>0.139975085223758</v>
       </c>
     </row>
     <row r="6">
@@ -3253,67 +3253,67 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>50539</v>
+        <v>60748</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>40457</v>
+        <v>49604</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>61234</v>
+        <v>72652</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.2544521659737448</v>
+        <v>0.2466063076191739</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.2036913858862814</v>
+        <v>0.2013681024497676</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.3083017428768302</v>
+        <v>0.294929348595827</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>37469</v>
+        <v>47186</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>29440</v>
+        <v>38053</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>47290</v>
+        <v>58351</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.2104073648825379</v>
+        <v>0.2174679454203492</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.1653193219369946</v>
+        <v>0.1753770698374699</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.2655568032185895</v>
+        <v>0.268920824344826</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>125</v>
+        <v>155</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>88008</v>
+        <v>107934</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>76498</v>
+        <v>93286</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>103205</v>
+        <v>125246</v>
       </c>
       <c r="U6" s="6" t="n">
-        <v>0.2336304672184801</v>
+        <v>0.2329601880439854</v>
       </c>
       <c r="V6" s="6" t="n">
-        <v>0.2030759563237194</v>
+        <v>0.2013427571602783</v>
       </c>
       <c r="W6" s="6" t="n">
-        <v>0.2739755309841056</v>
+        <v>0.2703243907483629</v>
       </c>
     </row>
     <row r="7">
@@ -3324,67 +3324,67 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>127</v>
+        <v>166</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>88901</v>
+        <v>117096</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>76165</v>
+        <v>104499</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>99711</v>
+        <v>130512</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.4476013665098632</v>
+        <v>0.475351867177192</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.3834749798885063</v>
+        <v>0.4242142038538841</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.5020265616195997</v>
+        <v>0.5298113792987753</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>105022</v>
+        <v>132236</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>93177</v>
+        <v>119930</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>115094</v>
+        <v>142638</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.5897498197357988</v>
+        <v>0.6094369982968816</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.5232319503674869</v>
+        <v>0.5527215859984507</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.6463069637918342</v>
+        <v>0.6573745602707735</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>287</v>
+        <v>366</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>193923</v>
+        <v>249333</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>177921</v>
+        <v>230444</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>209228</v>
+        <v>267041</v>
       </c>
       <c r="U7" s="6" t="n">
-        <v>0.5148004955391495</v>
+        <v>0.5381468080880409</v>
       </c>
       <c r="V7" s="6" t="n">
-        <v>0.4723190927408659</v>
+        <v>0.4973791339224384</v>
       </c>
       <c r="W7" s="6" t="n">
-        <v>0.5554284287808537</v>
+        <v>0.5763672377045433</v>
       </c>
     </row>
     <row r="8">
@@ -3401,19 +3401,19 @@
         <v>14221</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>8735</v>
+        <v>8300</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>20398</v>
+        <v>20487</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.07159820438994603</v>
+        <v>0.05772870652127597</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.04397755002010074</v>
+        <v>0.03369304126450683</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.1027003930145047</v>
+        <v>0.08316585052551791</v>
       </c>
       <c r="J8" s="5" t="n">
         <v>13</v>
@@ -3422,19 +3422,19 @@
         <v>8316</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>4502</v>
+        <v>4715</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>14046</v>
+        <v>13936</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.04670037457260857</v>
+        <v>0.03832755364538929</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.02528246098023225</v>
+        <v>0.02172816447904842</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.07887496896808664</v>
+        <v>0.06422527611627497</v>
       </c>
       <c r="Q8" s="5" t="n">
         <v>33</v>
@@ -3443,19 +3443,19 @@
         <v>22537</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>15552</v>
+        <v>15900</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>30333</v>
+        <v>31089</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.05982802722322605</v>
+        <v>0.04864273078131004</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>0.04128616024305694</v>
+        <v>0.03431848177762094</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.08052319716079287</v>
+        <v>0.06710116601137511</v>
       </c>
     </row>
     <row r="9">
@@ -3466,16 +3466,16 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>279</v>
+        <v>346</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>198617</v>
+        <v>246336</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>198617</v>
+        <v>246336</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>198617</v>
+        <v>246336</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>1</v>
@@ -3487,16 +3487,16 @@
         <v>1</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>271</v>
+        <v>329</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>178079</v>
+        <v>216981</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>178079</v>
+        <v>216981</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>178079</v>
+        <v>216981</v>
       </c>
       <c r="N9" s="6" t="n">
         <v>1</v>
@@ -3508,16 +3508,16 @@
         <v>1</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>550</v>
+        <v>675</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>376696</v>
+        <v>463317</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>376696</v>
+        <v>463317</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>376696</v>
+        <v>463317</v>
       </c>
       <c r="U9" s="6" t="n">
         <v>1</v>
@@ -3547,40 +3547,40 @@
         <v>14212</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>9188</v>
+        <v>9387</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>20621</v>
+        <v>20870</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.09508737902567185</v>
+        <v>0.08362739319911766</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.06147460914653949</v>
+        <v>0.05523777208967354</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.1379732135521633</v>
+        <v>0.122810312916881</v>
       </c>
       <c r="J10" s="5" t="n">
         <v>13</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>8669</v>
+        <v>8670</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>4690</v>
+        <v>5014</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>14556</v>
+        <v>14432</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.0597241404454224</v>
+        <v>0.05231239768002416</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.0323094939874233</v>
+        <v>0.03025316575529302</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.1002766091755211</v>
+        <v>0.08708298156729387</v>
       </c>
       <c r="Q10" s="5" t="n">
         <v>35</v>
@@ -3589,19 +3589,19 @@
         <v>22881</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>16507</v>
+        <v>16399</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>31348</v>
+        <v>31084</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.07766377896045336</v>
+        <v>0.06816645949164812</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.05602932734993334</v>
+        <v>0.0488561251885635</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.1064032347776422</v>
+        <v>0.09260533971106015</v>
       </c>
     </row>
     <row r="11">
@@ -3612,67 +3612,67 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>17987</v>
+        <v>20887</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>12177</v>
+        <v>14389</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>25179</v>
+        <v>29215</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.1203472175165827</v>
+        <v>0.1229067881581945</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.08147530774585852</v>
+        <v>0.08467210227546663</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.1684659347294705</v>
+        <v>0.1719150225931153</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>9399</v>
+        <v>10696</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>5192</v>
+        <v>6324</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>15376</v>
+        <v>18288</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.06475265142818636</v>
+        <v>0.06453908948818075</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.0357644305348988</v>
+        <v>0.03816046176296142</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.1059226497648788</v>
+        <v>0.1103491628414547</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="R11" s="5" t="n">
-        <v>27386</v>
+        <v>31583</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>20279</v>
+        <v>23577</v>
       </c>
       <c r="T11" s="5" t="n">
-        <v>36830</v>
+        <v>41754</v>
       </c>
       <c r="U11" s="6" t="n">
-        <v>0.09295556663241916</v>
+        <v>0.09408931254193857</v>
       </c>
       <c r="V11" s="6" t="n">
-        <v>0.06883286923252444</v>
+        <v>0.07023829964840692</v>
       </c>
       <c r="W11" s="6" t="n">
-        <v>0.1250078124993179</v>
+        <v>0.12439141678364</v>
       </c>
     </row>
     <row r="12">
@@ -3683,67 +3683,67 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>30732</v>
+        <v>39028</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>22817</v>
+        <v>30334</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>39296</v>
+        <v>48462</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.2056190443455548</v>
+        <v>0.2296589213809521</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.1526622587261021</v>
+        <v>0.1785006433161694</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.2629195007620143</v>
+        <v>0.2851708346116085</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>32581</v>
+        <v>38088</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>25018</v>
+        <v>30177</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>40987</v>
+        <v>47649</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.2244491648815152</v>
+        <v>0.2298256780805838</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.172350479170724</v>
+        <v>0.182090499346968</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.2823612719121585</v>
+        <v>0.2875155877437891</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>63312</v>
+        <v>77116</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>52038</v>
+        <v>65048</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>75803</v>
+        <v>89468</v>
       </c>
       <c r="U12" s="6" t="n">
-        <v>0.2148967152425204</v>
+        <v>0.2297412529998952</v>
       </c>
       <c r="V12" s="6" t="n">
-        <v>0.1766288266092793</v>
+        <v>0.193787235307721</v>
       </c>
       <c r="W12" s="6" t="n">
-        <v>0.2572925168469114</v>
+        <v>0.2665394953125889</v>
       </c>
     </row>
     <row r="13">
@@ -3754,67 +3754,67 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>77128</v>
+        <v>86412</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>66200</v>
+        <v>76215</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>86835</v>
+        <v>96875</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.5160469875509373</v>
+        <v>0.5084881942810783</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.4429277548395933</v>
+        <v>0.4484823379016799</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.5809981494762398</v>
+        <v>0.5700513822198592</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>89032</v>
+        <v>102795</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>78596</v>
+        <v>92122</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>97844</v>
+        <v>112395</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.6133400034186803</v>
+        <v>0.6202715746955614</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.5414465170493675</v>
+        <v>0.5558692137810854</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.6740457312581604</v>
+        <v>0.6781956612904335</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>242</v>
+        <v>277</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>166160</v>
+        <v>189208</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>151529</v>
+        <v>173458</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>180052</v>
+        <v>203110</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.5639836207801485</v>
+        <v>0.5636782208334181</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.5143230731491728</v>
+        <v>0.5167571668361799</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.6111361342251128</v>
+        <v>0.6050963172829875</v>
       </c>
     </row>
     <row r="14">
@@ -3831,19 +3831,19 @@
         <v>9401</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>5271</v>
+        <v>5002</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>15531</v>
+        <v>15745</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.06289937156125337</v>
+        <v>0.05531870298065742</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.03526637393052161</v>
+        <v>0.02943653399037239</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.10391380748841</v>
+        <v>0.09264781846056895</v>
       </c>
       <c r="J14" s="5" t="n">
         <v>8</v>
@@ -3852,19 +3852,19 @@
         <v>5477</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>2717</v>
+        <v>2603</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>10036</v>
+        <v>10282</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.03773403982619563</v>
+        <v>0.03305126005564993</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.01871551028795685</v>
+        <v>0.01570828363931558</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.06913459133151435</v>
+        <v>0.06204339246256813</v>
       </c>
       <c r="Q14" s="5" t="n">
         <v>21</v>
@@ -3873,19 +3873,19 @@
         <v>14878</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>9101</v>
+        <v>9679</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>21329</v>
+        <v>22225</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.0505003183844585</v>
+        <v>0.04432475413310005</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.03089235081914093</v>
+        <v>0.02883581370933512</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.07239637123774956</v>
+        <v>0.06621113906598658</v>
       </c>
     </row>
     <row r="15">
@@ -3896,16 +3896,16 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>214</v>
+        <v>243</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>149459</v>
+        <v>169940</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>149459</v>
+        <v>169940</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>149459</v>
+        <v>169940</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>1</v>
@@ -3917,16 +3917,16 @@
         <v>1</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>213</v>
+        <v>246</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>145159</v>
+        <v>165726</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>145159</v>
+        <v>165726</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>145159</v>
+        <v>165726</v>
       </c>
       <c r="N15" s="6" t="n">
         <v>1</v>
@@ -3938,16 +3938,16 @@
         <v>1</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>427</v>
+        <v>489</v>
       </c>
       <c r="R15" s="5" t="n">
-        <v>294618</v>
+        <v>335666</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>294618</v>
+        <v>335666</v>
       </c>
       <c r="T15" s="5" t="n">
-        <v>294618</v>
+        <v>335666</v>
       </c>
       <c r="U15" s="6" t="n">
         <v>1</v>
@@ -3977,19 +3977,19 @@
         <v>9890</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>5520</v>
+        <v>5834</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>15517</v>
+        <v>16363</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.09180430572787456</v>
+        <v>0.07830269478951273</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.05123859160772414</v>
+        <v>0.04618872762806406</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.1440418002482315</v>
+        <v>0.1295510028102942</v>
       </c>
       <c r="J16" s="5" t="n">
         <v>10</v>
@@ -3998,19 +3998,19 @@
         <v>6509</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>3237</v>
+        <v>3175</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>11113</v>
+        <v>11000</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.06109955241250711</v>
+        <v>0.0518769270160411</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.03038751611465321</v>
+        <v>0.02530867355146052</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.1043181485718644</v>
+        <v>0.08767517739033039</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>24</v>
@@ -4019,19 +4019,19 @@
         <v>16399</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>10692</v>
+        <v>10757</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>23701</v>
+        <v>24060</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>0.07653799868581042</v>
+        <v>0.06513380587355205</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>0.0499017257493808</v>
+        <v>0.04272681623084117</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>0.1106189452265393</v>
+        <v>0.09556337820222227</v>
       </c>
     </row>
     <row r="17">
@@ -4042,67 +4042,67 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>9556</v>
+        <v>11280</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>5604</v>
+        <v>6510</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>15445</v>
+        <v>17902</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.08870577215663067</v>
+        <v>0.08930863051182313</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.05202018551798902</v>
+        <v>0.05154304045397428</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.143370836856468</v>
+        <v>0.1417410478603297</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>10470</v>
+        <v>11651</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>6367</v>
+        <v>7456</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>16665</v>
+        <v>18262</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.09828241248654816</v>
+        <v>0.0928593989856589</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.05976944467427217</v>
+        <v>0.05942541139150902</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.1564404349518963</v>
+        <v>0.1455545780683004</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>20026</v>
+        <v>22930</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>13783</v>
+        <v>16105</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>27746</v>
+        <v>30408</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>0.09346724769125948</v>
+        <v>0.09107810324764198</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>0.06433200455094643</v>
+        <v>0.06396810601023653</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>0.1294996136859377</v>
+        <v>0.1207770514245197</v>
       </c>
     </row>
     <row r="18">
@@ -4113,67 +4113,67 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>28157</v>
+        <v>34859</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>21144</v>
+        <v>27028</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>36572</v>
+        <v>43982</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.2613742899063222</v>
+        <v>0.27599704598706</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.196276005104261</v>
+        <v>0.2139931966884367</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0.3394852087640647</v>
+        <v>0.3482284838580968</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>20216</v>
+        <v>24319</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>14333</v>
+        <v>18579</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>27448</v>
+        <v>32674</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.1897756575429158</v>
+        <v>0.1938307810721551</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.1345495343085524</v>
+        <v>0.148081269413487</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.2576660727202301</v>
+        <v>0.2604249686065809</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="R18" s="5" t="n">
-        <v>48373</v>
+        <v>59178</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>39692</v>
+        <v>47551</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>59415</v>
+        <v>70874</v>
       </c>
       <c r="U18" s="6" t="n">
-        <v>0.2257756744663938</v>
+        <v>0.2350507081330651</v>
       </c>
       <c r="V18" s="6" t="n">
-        <v>0.185258450234879</v>
+        <v>0.1888699506932706</v>
       </c>
       <c r="W18" s="6" t="n">
-        <v>0.2773119127507402</v>
+        <v>0.2815045325291575</v>
       </c>
     </row>
     <row r="19">
@@ -4184,67 +4184,67 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>53719</v>
+        <v>63868</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>44358</v>
+        <v>54737</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>62397</v>
+        <v>73032</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.498649859593687</v>
+        <v>0.5056714559853359</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>0.4117625422546334</v>
+        <v>0.4333755814612418</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.5792055265950853</v>
+        <v>0.5782256357643467</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>65928</v>
+        <v>79583</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>56758</v>
+        <v>70482</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>73377</v>
+        <v>87938</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.6188937659434097</v>
+        <v>0.6343067401549148</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.5328121939534708</v>
+        <v>0.5617692922229709</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.6888161304931293</v>
+        <v>0.7008983527049405</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>174</v>
+        <v>209</v>
       </c>
       <c r="R19" s="5" t="n">
-        <v>119647</v>
+        <v>143451</v>
       </c>
       <c r="S19" s="5" t="n">
-        <v>105890</v>
+        <v>131105</v>
       </c>
       <c r="T19" s="5" t="n">
-        <v>131509</v>
+        <v>156374</v>
       </c>
       <c r="U19" s="6" t="n">
-        <v>0.5584347526823193</v>
+        <v>0.5697749394649259</v>
       </c>
       <c r="V19" s="6" t="n">
-        <v>0.4942244710435005</v>
+        <v>0.5207400297847742</v>
       </c>
       <c r="W19" s="6" t="n">
-        <v>0.6138012033472482</v>
+        <v>0.6211066148339143</v>
       </c>
     </row>
     <row r="20">
@@ -4261,19 +4261,19 @@
         <v>6406</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>2849</v>
+        <v>2702</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>11940</v>
+        <v>12014</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.05946577261548561</v>
+        <v>0.05072017272626823</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.02644617477992449</v>
+        <v>0.02139042726299564</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.1108314439505213</v>
+        <v>0.09512088466032136</v>
       </c>
       <c r="J20" s="5" t="n">
         <v>5</v>
@@ -4282,19 +4282,19 @@
         <v>3403</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>1186</v>
+        <v>1303</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>7708</v>
+        <v>7578</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.03194861161461925</v>
+        <v>0.02712615277123005</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.01113415187627329</v>
+        <v>0.0103836230252901</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.07236237246336837</v>
+        <v>0.06040271377925388</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>13</v>
@@ -4303,19 +4303,19 @@
         <v>9809</v>
       </c>
       <c r="S20" s="5" t="n">
-        <v>5445</v>
+        <v>5007</v>
       </c>
       <c r="T20" s="5" t="n">
-        <v>16318</v>
+        <v>16041</v>
       </c>
       <c r="U20" s="6" t="n">
-        <v>0.04578432647421699</v>
+        <v>0.03896244328081497</v>
       </c>
       <c r="V20" s="6" t="n">
-        <v>0.02541503280864393</v>
+        <v>0.01988692618928128</v>
       </c>
       <c r="W20" s="6" t="n">
-        <v>0.07616127845565186</v>
+        <v>0.06371209501629352</v>
       </c>
     </row>
     <row r="21">
@@ -4326,16 +4326,16 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>155</v>
+        <v>182</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>107728</v>
+        <v>126303</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>107728</v>
+        <v>126303</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>107728</v>
+        <v>126303</v>
       </c>
       <c r="G21" s="6" t="n">
         <v>1</v>
@@ -4347,16 +4347,16 @@
         <v>1</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>157</v>
+        <v>185</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>106526</v>
+        <v>125465</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>106526</v>
+        <v>125465</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>106526</v>
+        <v>125465</v>
       </c>
       <c r="N21" s="6" t="n">
         <v>1</v>
@@ -4368,16 +4368,16 @@
         <v>1</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>312</v>
+        <v>367</v>
       </c>
       <c r="R21" s="5" t="n">
-        <v>214254</v>
+        <v>251767</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>214254</v>
+        <v>251767</v>
       </c>
       <c r="T21" s="5" t="n">
-        <v>214254</v>
+        <v>251767</v>
       </c>
       <c r="U21" s="6" t="n">
         <v>1</v>
@@ -4407,19 +4407,19 @@
         <v>6140</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>2764</v>
+        <v>3355</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>10651</v>
+        <v>11044</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.0977024087404203</v>
+        <v>0.07366844270060682</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.04398572213760436</v>
+        <v>0.04025047955201515</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.1694626730603201</v>
+        <v>0.1325015761969616</v>
       </c>
       <c r="J22" s="5" t="n">
         <v>4</v>
@@ -4428,19 +4428,19 @@
         <v>2421</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>630</v>
+        <v>676</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>6398</v>
+        <v>6201</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.04729579137538108</v>
+        <v>0.03912571843615983</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.01230040517717494</v>
+        <v>0.01092119576535076</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.1250117330486533</v>
+        <v>0.1002352778154245</v>
       </c>
       <c r="Q22" s="5" t="n">
         <v>13</v>
@@ -4449,19 +4449,19 @@
         <v>8561</v>
       </c>
       <c r="S22" s="5" t="n">
-        <v>4580</v>
+        <v>5153</v>
       </c>
       <c r="T22" s="5" t="n">
-        <v>13816</v>
+        <v>14074</v>
       </c>
       <c r="U22" s="6" t="n">
-        <v>0.075078239797994</v>
+        <v>0.05895244861633674</v>
       </c>
       <c r="V22" s="6" t="n">
-        <v>0.0401687770546922</v>
+        <v>0.0354869291360991</v>
       </c>
       <c r="W22" s="6" t="n">
-        <v>0.1211615817661647</v>
+        <v>0.09691714520843028</v>
       </c>
     </row>
     <row r="23">
@@ -4472,67 +4472,67 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>7740</v>
+        <v>9216</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>4025</v>
+        <v>4972</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>13128</v>
+        <v>14665</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.1231455624929454</v>
+        <v>0.1105657471352843</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.06404901479387444</v>
+        <v>0.05964427412303425</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.2088862923306166</v>
+        <v>0.1759380159933141</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>2430</v>
+        <v>4232</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>675</v>
+        <v>1781</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>6250</v>
+        <v>8203</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.04747609056220868</v>
+        <v>0.06840262291669075</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.01317988723101661</v>
+        <v>0.02878694322933186</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.1221246604783397</v>
+        <v>0.132595095092763</v>
       </c>
       <c r="Q23" s="5" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="R23" s="5" t="n">
-        <v>10169</v>
+        <v>13448</v>
       </c>
       <c r="S23" s="5" t="n">
-        <v>5744</v>
+        <v>8619</v>
       </c>
       <c r="T23" s="5" t="n">
-        <v>15961</v>
+        <v>19963</v>
       </c>
       <c r="U23" s="6" t="n">
-        <v>0.08918258290343334</v>
+        <v>0.09260328760762665</v>
       </c>
       <c r="V23" s="6" t="n">
-        <v>0.05037546328961277</v>
+        <v>0.05935405506329653</v>
       </c>
       <c r="W23" s="6" t="n">
-        <v>0.1399778028291546</v>
+        <v>0.137469212729538</v>
       </c>
     </row>
     <row r="24">
@@ -4543,67 +4543,67 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>14958</v>
+        <v>20596</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>10079</v>
+        <v>13977</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>21869</v>
+        <v>26995</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>0.2380062002897831</v>
+        <v>0.2470915848364507</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>0.1603688930914812</v>
+        <v>0.1676895043798235</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>0.3479688955533444</v>
+        <v>0.3238656800299655</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>10732</v>
+        <v>12597</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>6437</v>
+        <v>7889</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>16604</v>
+        <v>19019</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>0.2096824426633634</v>
+        <v>0.2036076265354068</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.1257700500938281</v>
+        <v>0.1275214839991472</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.324422550210187</v>
+        <v>0.3074194539675862</v>
       </c>
       <c r="Q24" s="5" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="R24" s="5" t="n">
-        <v>25690</v>
+        <v>33192</v>
       </c>
       <c r="S24" s="5" t="n">
-        <v>18631</v>
+        <v>25692</v>
       </c>
       <c r="T24" s="5" t="n">
-        <v>33964</v>
+        <v>42341</v>
       </c>
       <c r="U24" s="6" t="n">
-        <v>0.2252935543888721</v>
+        <v>0.2285664196462391</v>
       </c>
       <c r="V24" s="6" t="n">
-        <v>0.1633876751896958</v>
+        <v>0.1769176816112999</v>
       </c>
       <c r="W24" s="6" t="n">
-        <v>0.2978537253816721</v>
+        <v>0.2915667491582346</v>
       </c>
     </row>
     <row r="25">
@@ -4614,67 +4614,67 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>33271</v>
+        <v>46662</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>26826</v>
+        <v>38904</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>39317</v>
+        <v>54231</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0.5293851594544584</v>
+        <v>0.5598065813957793</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.4268344398725378</v>
+        <v>0.4667367149553682</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.6255794185551641</v>
+        <v>0.650619996683993</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>33786</v>
+        <v>40806</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>28107</v>
+        <v>34592</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>39342</v>
+        <v>46563</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.6601335539993053</v>
+        <v>0.6595691487654286</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.5491706518653099</v>
+        <v>0.5591407614515107</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.7687080233885512</v>
+        <v>0.7526278257544989</v>
       </c>
       <c r="Q25" s="5" t="n">
-        <v>95</v>
+        <v>125</v>
       </c>
       <c r="R25" s="5" t="n">
-        <v>67056</v>
+        <v>87467</v>
       </c>
       <c r="S25" s="5" t="n">
-        <v>57982</v>
+        <v>77670</v>
       </c>
       <c r="T25" s="5" t="n">
-        <v>75363</v>
+        <v>97075</v>
       </c>
       <c r="U25" s="6" t="n">
-        <v>0.5880693942189453</v>
+        <v>0.6023077269338108</v>
       </c>
       <c r="V25" s="6" t="n">
-        <v>0.5084869320238304</v>
+        <v>0.5348431375662861</v>
       </c>
       <c r="W25" s="6" t="n">
-        <v>0.660917139412853</v>
+        <v>0.6684656473922818</v>
       </c>
     </row>
     <row r="26">
@@ -4694,16 +4694,16 @@
         <v>0</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>3101</v>
+        <v>3726</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.01176066902239273</v>
+        <v>0.008867643931878909</v>
       </c>
       <c r="H26" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.04933520287237764</v>
+        <v>0.04470163629735816</v>
       </c>
       <c r="J26" s="5" t="n">
         <v>3</v>
@@ -4712,19 +4712,19 @@
         <v>1812</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>560</v>
+        <v>551</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>4823</v>
+        <v>4688</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.03541212139974149</v>
+        <v>0.02929488334631407</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.01094493635023758</v>
+        <v>0.008912539935235813</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.09422918947890487</v>
+        <v>0.07577551898204532</v>
       </c>
       <c r="Q26" s="5" t="n">
         <v>4</v>
@@ -4733,19 +4733,19 @@
         <v>2552</v>
       </c>
       <c r="S26" s="5" t="n">
-        <v>738</v>
+        <v>617</v>
       </c>
       <c r="T26" s="5" t="n">
-        <v>6130</v>
+        <v>5989</v>
       </c>
       <c r="U26" s="6" t="n">
-        <v>0.02237622869075518</v>
+        <v>0.01757011719598667</v>
       </c>
       <c r="V26" s="6" t="n">
-        <v>0.00646983118675571</v>
+        <v>0.004248255499442956</v>
       </c>
       <c r="W26" s="6" t="n">
-        <v>0.05375590956607709</v>
+        <v>0.04124176611276561</v>
       </c>
     </row>
     <row r="27">
@@ -4756,16 +4756,16 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>88</v>
+        <v>117</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>62849</v>
+        <v>83353</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>62849</v>
+        <v>83353</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>62849</v>
+        <v>83353</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>1</v>
@@ -4777,16 +4777,16 @@
         <v>1</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>51180</v>
+        <v>61867</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>51180</v>
+        <v>61867</v>
       </c>
       <c r="M27" s="5" t="n">
-        <v>51180</v>
+        <v>61867</v>
       </c>
       <c r="N27" s="6" t="n">
         <v>1</v>
@@ -4798,16 +4798,16 @@
         <v>1</v>
       </c>
       <c r="Q27" s="5" t="n">
-        <v>163</v>
+        <v>209</v>
       </c>
       <c r="R27" s="5" t="n">
-        <v>114028</v>
+        <v>145220</v>
       </c>
       <c r="S27" s="5" t="n">
-        <v>114028</v>
+        <v>145220</v>
       </c>
       <c r="T27" s="5" t="n">
-        <v>114028</v>
+        <v>145220</v>
       </c>
       <c r="U27" s="6" t="n">
         <v>1</v>
@@ -4837,19 +4837,19 @@
         <v>49893</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>39651</v>
+        <v>39457</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>61844</v>
+        <v>61044</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0.09619753343640217</v>
+        <v>0.0797101344796655</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>0.07644968595202452</v>
+        <v>0.06303804514766038</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>0.1192405436095974</v>
+        <v>0.09752462267745861</v>
       </c>
       <c r="J28" s="5" t="n">
         <v>45</v>
@@ -4858,19 +4858,19 @@
         <v>28947</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>21809</v>
+        <v>21564</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>37686</v>
+        <v>38235</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.06018853409383264</v>
+        <v>0.05078139011145155</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.04534633242253778</v>
+        <v>0.03782823386093324</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.07835726658252577</v>
+        <v>0.06707473535210846</v>
       </c>
       <c r="Q28" s="5" t="n">
         <v>117</v>
@@ -4879,19 +4879,19 @@
         <v>78840</v>
       </c>
       <c r="S28" s="5" t="n">
-        <v>66486</v>
+        <v>65296</v>
       </c>
       <c r="T28" s="5" t="n">
-        <v>93506</v>
+        <v>94258</v>
       </c>
       <c r="U28" s="6" t="n">
-        <v>0.07887221177829193</v>
+        <v>0.06592174103579965</v>
       </c>
       <c r="V28" s="6" t="n">
-        <v>0.06651244370182742</v>
+        <v>0.05459672561735836</v>
       </c>
       <c r="W28" s="6" t="n">
-        <v>0.09354355800287241</v>
+        <v>0.07881297497318394</v>
       </c>
     </row>
     <row r="29">
@@ -4902,67 +4902,67 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>60588</v>
+        <v>76003</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>48947</v>
+        <v>62727</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>73958</v>
+        <v>90171</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0.1168183564153282</v>
+        <v>0.1214231486764336</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>0.09437260034481838</v>
+        <v>0.1002145731962973</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>0.1425971178336625</v>
+        <v>0.1440589122220504</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>38222</v>
+        <v>44472</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>29666</v>
+        <v>35375</v>
       </c>
       <c r="M29" s="5" t="n">
-        <v>48433</v>
+        <v>55795</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.07947250319473134</v>
+        <v>0.07801525480138093</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.06168200252567144</v>
+        <v>0.06205653312720302</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.1007041975991859</v>
+        <v>0.09787878606497014</v>
       </c>
       <c r="Q29" s="5" t="n">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="R29" s="5" t="n">
-        <v>98810</v>
+        <v>120474</v>
       </c>
       <c r="S29" s="5" t="n">
-        <v>84885</v>
+        <v>104760</v>
       </c>
       <c r="T29" s="5" t="n">
-        <v>115277</v>
+        <v>140141</v>
       </c>
       <c r="U29" s="6" t="n">
-        <v>0.09884982267497232</v>
+        <v>0.1007335151513629</v>
       </c>
       <c r="V29" s="6" t="n">
-        <v>0.08491957379178676</v>
+        <v>0.08759393023003588</v>
       </c>
       <c r="W29" s="6" t="n">
-        <v>0.1153238853953487</v>
+        <v>0.1171774746566563</v>
       </c>
     </row>
     <row r="30">
@@ -4973,67 +4973,67 @@
         </is>
       </c>
       <c r="C30" s="5" t="n">
-        <v>175</v>
+        <v>220</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>124386</v>
+        <v>155231</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>107849</v>
+        <v>137387</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>139813</v>
+        <v>172110</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.239824943897404</v>
+        <v>0.2480003013512349</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>0.2079411010461332</v>
+        <v>0.2194924348151227</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>0.2695696997776961</v>
+        <v>0.2749656319932535</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>147</v>
+        <v>180</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>100998</v>
+        <v>122190</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>86420</v>
+        <v>106945</v>
       </c>
       <c r="M30" s="5" t="n">
-        <v>115735</v>
+        <v>139679</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.2099985410326186</v>
+        <v>0.2143539062556733</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.1796875801244936</v>
+        <v>0.1876096531781168</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.2406413565840033</v>
+        <v>0.2450344522588594</v>
       </c>
       <c r="Q30" s="5" t="n">
-        <v>322</v>
+        <v>400</v>
       </c>
       <c r="R30" s="5" t="n">
-        <v>225383</v>
+        <v>277421</v>
       </c>
       <c r="S30" s="5" t="n">
-        <v>204197</v>
+        <v>256049</v>
       </c>
       <c r="T30" s="5" t="n">
-        <v>248476</v>
+        <v>302209</v>
       </c>
       <c r="U30" s="6" t="n">
-        <v>0.2254743084181812</v>
+        <v>0.2319633200139075</v>
       </c>
       <c r="V30" s="6" t="n">
-        <v>0.204279004363706</v>
+        <v>0.2140929523229172</v>
       </c>
       <c r="W30" s="6" t="n">
-        <v>0.2485760788132348</v>
+        <v>0.2526894670208556</v>
       </c>
     </row>
     <row r="31">
@@ -5044,67 +5044,67 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>361</v>
+        <v>447</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>253018</v>
+        <v>314038</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>233466</v>
+        <v>295042</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>269551</v>
+        <v>337140</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.4878386011022022</v>
+        <v>0.5017128659524818</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0.4501403032915436</v>
+        <v>0.4713646818078206</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>0.5197142935152302</v>
+        <v>0.5386217426175334</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>437</v>
+        <v>530</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>293768</v>
+        <v>355420</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>275770</v>
+        <v>337862</v>
       </c>
       <c r="M31" s="5" t="n">
-        <v>310789</v>
+        <v>375934</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.6108149489206183</v>
+        <v>0.6235015947643966</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.5733915506206362</v>
+        <v>0.5926997633896375</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.646205552515317</v>
+        <v>0.6594884261072487</v>
       </c>
       <c r="Q31" s="5" t="n">
-        <v>798</v>
+        <v>977</v>
       </c>
       <c r="R31" s="5" t="n">
-        <v>546787</v>
+        <v>669458</v>
       </c>
       <c r="S31" s="5" t="n">
-        <v>519721</v>
+        <v>639155</v>
       </c>
       <c r="T31" s="5" t="n">
-        <v>572036</v>
+        <v>697038</v>
       </c>
       <c r="U31" s="6" t="n">
-        <v>0.5470072761887914</v>
+        <v>0.5597613898881454</v>
       </c>
       <c r="V31" s="6" t="n">
-        <v>0.5199305290590779</v>
+        <v>0.534423933639339</v>
       </c>
       <c r="W31" s="6" t="n">
-        <v>0.5722663856073479</v>
+        <v>0.5828223206195076</v>
       </c>
     </row>
     <row r="32">
@@ -5121,19 +5121,19 @@
         <v>30767</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>22388</v>
+        <v>22782</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>39868</v>
+        <v>41179</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>0.05932056514866348</v>
+        <v>0.04915354954018425</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>0.04316646499280799</v>
+        <v>0.03639721016146707</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>0.07686881937419901</v>
+        <v>0.06578845556893929</v>
       </c>
       <c r="J32" s="5" t="n">
         <v>29</v>
@@ -5142,19 +5142,19 @@
         <v>19010</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>12687</v>
+        <v>12265</v>
       </c>
       <c r="M32" s="5" t="n">
-        <v>26281</v>
+        <v>26204</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.03952547275819914</v>
+        <v>0.03334785406709763</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.02638001860433356</v>
+        <v>0.02151649565300033</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.05464539792894826</v>
+        <v>0.04596919121636831</v>
       </c>
       <c r="Q32" s="5" t="n">
         <v>71</v>
@@ -5163,19 +5163,19 @@
         <v>49776</v>
       </c>
       <c r="S32" s="5" t="n">
-        <v>39593</v>
+        <v>39795</v>
       </c>
       <c r="T32" s="5" t="n">
-        <v>61917</v>
+        <v>63160</v>
       </c>
       <c r="U32" s="6" t="n">
-        <v>0.0497963809397631</v>
+        <v>0.04162003391078458</v>
       </c>
       <c r="V32" s="6" t="n">
-        <v>0.0396090469579248</v>
+        <v>0.03327391026838972</v>
       </c>
       <c r="W32" s="6" t="n">
-        <v>0.06194181871308607</v>
+        <v>0.05281042560302519</v>
       </c>
     </row>
     <row r="33">
@@ -5186,16 +5186,16 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>736</v>
+        <v>888</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>518652</v>
+        <v>625931</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>518652</v>
+        <v>625931</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>518652</v>
+        <v>625931</v>
       </c>
       <c r="G33" s="6" t="n">
         <v>1</v>
@@ -5207,16 +5207,16 @@
         <v>1</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>716</v>
+        <v>852</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>480945</v>
+        <v>570039</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>480945</v>
+        <v>570039</v>
       </c>
       <c r="M33" s="5" t="n">
-        <v>480945</v>
+        <v>570039</v>
       </c>
       <c r="N33" s="6" t="n">
         <v>1</v>
@@ -5228,16 +5228,16 @@
         <v>1</v>
       </c>
       <c r="Q33" s="5" t="n">
-        <v>1452</v>
+        <v>1740</v>
       </c>
       <c r="R33" s="5" t="n">
-        <v>999597</v>
+        <v>1195970</v>
       </c>
       <c r="S33" s="5" t="n">
-        <v>999597</v>
+        <v>1195970</v>
       </c>
       <c r="T33" s="5" t="n">
-        <v>999597</v>
+        <v>1195970</v>
       </c>
       <c r="U33" s="6" t="n">
         <v>1</v>
@@ -5309,7 +5309,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la categoría de IMC recogido por medición en 2023 (tasa de respuesta: 78,24%)</t>
+          <t>Menores según la categoría de IMC recogido por medición en 2023 (tasa de respuesta: 82,23%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5499,19 +5499,19 @@
         <v>5385</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>2473</v>
+        <v>2299</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>10143</v>
+        <v>9979</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.1267646162445736</v>
+        <v>0.1190201032268343</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.05821490969633249</v>
+        <v>0.05082608094744097</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.2387920438999423</v>
+        <v>0.2205810563567998</v>
       </c>
       <c r="J4" s="5" t="n">
         <v>3</v>
@@ -5520,19 +5520,19 @@
         <v>1392</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>4042</v>
+        <v>3889</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.04482940494622842</v>
+        <v>0.04138427222115573</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.01052018188448923</v>
+        <v>0.009532818688327454</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.1302007634207615</v>
+        <v>0.1156483409897572</v>
       </c>
       <c r="Q4" s="5" t="n">
         <v>12</v>
@@ -5541,19 +5541,19 @@
         <v>6776</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>3421</v>
+        <v>3660</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>11609</v>
+        <v>12163</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>0.09216594271782377</v>
+        <v>0.08591597353707263</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>0.04653501596676021</v>
+        <v>0.0463995374433766</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>0.1578921935206661</v>
+        <v>0.1542177413403413</v>
       </c>
     </row>
     <row r="5">
@@ -5564,67 +5564,67 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>8571</v>
+        <v>9026</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>4189</v>
+        <v>4299</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>15541</v>
+        <v>15596</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.201781208025936</v>
+        <v>0.1995150088645445</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.09861467610224683</v>
+        <v>0.09503466224602526</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.3658629736575536</v>
+        <v>0.3447325920302893</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>3662</v>
+        <v>4231</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>1368</v>
+        <v>1619</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>8045</v>
+        <v>8411</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.1179488664452168</v>
+        <v>0.1258111573123101</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.04405526332621543</v>
+        <v>0.04812558857004628</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.2591222352262345</v>
+        <v>0.2501085991190398</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>12233</v>
+        <v>13257</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>6401</v>
+        <v>7762</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>19285</v>
+        <v>20633</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.1663814357989148</v>
+        <v>0.1680874859178055</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>0.08705674599750543</v>
+        <v>0.09841487325804668</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>0.2622910830642305</v>
+        <v>0.2616036773856962</v>
       </c>
     </row>
     <row r="6">
@@ -5635,67 +5635,67 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>9234</v>
+        <v>9830</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>5274</v>
+        <v>5608</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>14456</v>
+        <v>15021</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.2173837640067031</v>
+        <v>0.217285779136875</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.1241705297437826</v>
+        <v>0.1239550569682174</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.3403239972514596</v>
+        <v>0.3320325972340518</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>2958</v>
+        <v>4277</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>886</v>
+        <v>1859</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>6813</v>
+        <v>8974</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.09527071194390491</v>
+        <v>0.1271653785966956</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.02854308070394945</v>
+        <v>0.05526394614360316</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.2194438262151996</v>
+        <v>0.2668468600895538</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>12192</v>
+        <v>14107</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>7322</v>
+        <v>8655</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>18827</v>
+        <v>20155</v>
       </c>
       <c r="U6" s="6" t="n">
-        <v>0.1658192466920198</v>
+        <v>0.1788581950107109</v>
       </c>
       <c r="V6" s="6" t="n">
-        <v>0.09958776634161404</v>
+        <v>0.1097327206407654</v>
       </c>
       <c r="W6" s="6" t="n">
-        <v>0.256061980558172</v>
+        <v>0.25554277943415</v>
       </c>
     </row>
     <row r="7">
@@ -5706,67 +5706,67 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>19288</v>
+        <v>21000</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>13586</v>
+        <v>15298</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>25546</v>
+        <v>27501</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.4540704117227873</v>
+        <v>0.4641791087717462</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.3198517271105141</v>
+        <v>0.338154610032661</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.6014169069946765</v>
+        <v>0.6078687667255108</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>22400</v>
+        <v>23096</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>17948</v>
+        <v>18455</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>26186</v>
+        <v>27376</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.7214969386627605</v>
+        <v>0.6867570065479883</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.5780987850077279</v>
+        <v>0.5487487908563273</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.8434258029528132</v>
+        <v>0.8140078252549096</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>41688</v>
+        <v>44096</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>34364</v>
+        <v>36227</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>49458</v>
+        <v>52278</v>
       </c>
       <c r="U7" s="6" t="n">
-        <v>0.5669962582711997</v>
+        <v>0.5590869303099777</v>
       </c>
       <c r="V7" s="6" t="n">
-        <v>0.4673810333367248</v>
+        <v>0.459310082261824</v>
       </c>
       <c r="W7" s="6" t="n">
-        <v>0.6726809790532903</v>
+        <v>0.662825157553571</v>
       </c>
     </row>
     <row r="8">
@@ -5799,16 +5799,16 @@
         <v>0</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>2968</v>
+        <v>2846</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.02045407800188949</v>
+        <v>0.01888218532185008</v>
       </c>
       <c r="O8" s="6" t="n">
         <v>0</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.09558324482585545</v>
+        <v>0.08462250993053035</v>
       </c>
       <c r="Q8" s="5" t="n">
         <v>1</v>
@@ -5820,16 +5820,16 @@
         <v>0</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>2912</v>
+        <v>3322</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.008637116520041748</v>
+        <v>0.008051415224433147</v>
       </c>
       <c r="V8" s="6" t="n">
         <v>0</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.03960474268191853</v>
+        <v>0.0421163159536977</v>
       </c>
     </row>
     <row r="9">
@@ -5840,16 +5840,16 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>42477</v>
+        <v>45241</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>42477</v>
+        <v>45241</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>42477</v>
+        <v>45241</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>1</v>
@@ -5861,16 +5861,16 @@
         <v>1</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>31047</v>
+        <v>33631</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>31047</v>
+        <v>33631</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>31047</v>
+        <v>33631</v>
       </c>
       <c r="N9" s="6" t="n">
         <v>1</v>
@@ -5882,16 +5882,16 @@
         <v>1</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>73524</v>
+        <v>78872</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>73524</v>
+        <v>78872</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>73524</v>
+        <v>78872</v>
       </c>
       <c r="U9" s="6" t="n">
         <v>1</v>
@@ -5921,19 +5921,19 @@
         <v>5586</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>2669</v>
+        <v>2480</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>10989</v>
+        <v>10300</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.06089120054134604</v>
+        <v>0.05829926556276614</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.02909179304685582</v>
+        <v>0.02588253316255831</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.1197864644058171</v>
+        <v>0.1074960674855554</v>
       </c>
       <c r="J10" s="5" t="n">
         <v>5</v>
@@ -5942,19 +5942,19 @@
         <v>3279</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>1010</v>
+        <v>1129</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>6949</v>
+        <v>7359</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.04944098339632603</v>
+        <v>0.04617515144541762</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.01522394131663488</v>
+        <v>0.01590030075895246</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.1047834601082179</v>
+        <v>0.1036383748205805</v>
       </c>
       <c r="Q10" s="5" t="n">
         <v>14</v>
@@ -5963,19 +5963,19 @@
         <v>8865</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>4843</v>
+        <v>5052</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>14847</v>
+        <v>14485</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.05608720624447684</v>
+        <v>0.05313905344901255</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.03063849824965561</v>
+        <v>0.03028552096527605</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.0939342845627149</v>
+        <v>0.0868315240648227</v>
       </c>
     </row>
     <row r="11">
@@ -5992,61 +5992,61 @@
         <v>8447</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>4498</v>
+        <v>4601</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>14346</v>
+        <v>14833</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.09207512785016779</v>
+        <v>0.08815579726692502</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.04902341756752967</v>
+        <v>0.04801153352753785</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.1563745419546239</v>
+        <v>0.1548004003244931</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>4801</v>
+        <v>5623</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>1979</v>
+        <v>2561</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>9602</v>
+        <v>10486</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.07239173406451131</v>
+        <v>0.07919886472539148</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.02983763826468185</v>
+        <v>0.03606497659637871</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.1448035492199083</v>
+        <v>0.1476797332883493</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R11" s="5" t="n">
-        <v>13248</v>
+        <v>14070</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>8074</v>
+        <v>9274</v>
       </c>
       <c r="T11" s="5" t="n">
-        <v>20565</v>
+        <v>21249</v>
       </c>
       <c r="U11" s="6" t="n">
-        <v>0.08381686424767791</v>
+        <v>0.08434358704228198</v>
       </c>
       <c r="V11" s="6" t="n">
-        <v>0.05108610010813593</v>
+        <v>0.05559057861579617</v>
       </c>
       <c r="W11" s="6" t="n">
-        <v>0.1301117785661144</v>
+        <v>0.1273729824989342</v>
       </c>
     </row>
     <row r="12">
@@ -6057,25 +6057,25 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>21026</v>
+        <v>22272</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>13713</v>
+        <v>14672</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>33640</v>
+        <v>34692</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.229182335417973</v>
+        <v>0.2324284988381318</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.1494776156540189</v>
+        <v>0.1531229424528296</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.3666816450514636</v>
+        <v>0.3620502803991702</v>
       </c>
       <c r="J12" s="5" t="n">
         <v>19</v>
@@ -6084,40 +6084,40 @@
         <v>12550</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>7559</v>
+        <v>7940</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>18649</v>
+        <v>19454</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.1892518036141691</v>
+        <v>0.1767507458974222</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.1139847489986503</v>
+        <v>0.1118325844214526</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.2812230121240641</v>
+        <v>0.2739856684860107</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>33576</v>
+        <v>34821</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>24210</v>
+        <v>25777</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>46621</v>
+        <v>48432</v>
       </c>
       <c r="U12" s="6" t="n">
-        <v>0.2124292865782085</v>
+        <v>0.2087311785712337</v>
       </c>
       <c r="V12" s="6" t="n">
-        <v>0.1531720473744424</v>
+        <v>0.1545165089927763</v>
       </c>
       <c r="W12" s="6" t="n">
-        <v>0.2949667744211617</v>
+        <v>0.2903188946699408</v>
       </c>
     </row>
     <row r="13">
@@ -6128,67 +6128,67 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>51381</v>
+        <v>54214</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>40772</v>
+        <v>43127</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>59956</v>
+        <v>62655</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.56006276868524</v>
+        <v>0.5657877370825749</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.4444195405959132</v>
+        <v>0.4500738136398953</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.6535291412913345</v>
+        <v>0.6538722441806919</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>43184</v>
+        <v>47051</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>36325</v>
+        <v>40484</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>49742</v>
+        <v>53504</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.6512181719486504</v>
+        <v>0.6626680325094269</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.5477813418764366</v>
+        <v>0.5701723841811431</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.7501084349383258</v>
+        <v>0.753538743496238</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>94565</v>
+        <v>101265</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>82615</v>
+        <v>88465</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>106415</v>
+        <v>111804</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.5983074615028515</v>
+        <v>0.6070215022226044</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.522696480117678</v>
+        <v>0.5302919501141146</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.6732776301104931</v>
+        <v>0.6701935428307374</v>
       </c>
     </row>
     <row r="14">
@@ -6205,19 +6205,19 @@
         <v>5302</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>2478</v>
+        <v>2440</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>10982</v>
+        <v>10966</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.05778856750527318</v>
+        <v>0.05532870124960232</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.02701440539751508</v>
+        <v>0.02546374278480129</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.1197052053729621</v>
+        <v>0.1144447769253726</v>
       </c>
       <c r="J14" s="5" t="n">
         <v>4</v>
@@ -6226,19 +6226,19 @@
         <v>2500</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>654</v>
+        <v>605</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>6005</v>
+        <v>5881</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.03769730697634315</v>
+        <v>0.03520720542234184</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.009860408075270883</v>
+        <v>0.008526783353026157</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.09055671273621743</v>
+        <v>0.08283255539028898</v>
       </c>
       <c r="Q14" s="5" t="n">
         <v>11</v>
@@ -6247,19 +6247,19 @@
         <v>7801</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>3963</v>
+        <v>4107</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>13302</v>
+        <v>13663</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.04935918142678544</v>
+        <v>0.04676467871486732</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.02507450949393426</v>
+        <v>0.02461704561576721</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.0841633713798043</v>
+        <v>0.08189976476220151</v>
       </c>
     </row>
     <row r="15">
@@ -6270,16 +6270,16 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>91742</v>
+        <v>95821</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>91742</v>
+        <v>95821</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>91742</v>
+        <v>95821</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>1</v>
@@ -6291,16 +6291,16 @@
         <v>1</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>66313</v>
+        <v>71003</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>66313</v>
+        <v>71003</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>66313</v>
+        <v>71003</v>
       </c>
       <c r="N15" s="6" t="n">
         <v>1</v>
@@ -6312,16 +6312,16 @@
         <v>1</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="R15" s="5" t="n">
-        <v>158055</v>
+        <v>166823</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>158055</v>
+        <v>166823</v>
       </c>
       <c r="T15" s="5" t="n">
-        <v>158055</v>
+        <v>166823</v>
       </c>
       <c r="U15" s="6" t="n">
         <v>1</v>
@@ -6351,19 +6351,19 @@
         <v>6241</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>3153</v>
+        <v>3014</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>11298</v>
+        <v>11341</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.06208571219510622</v>
+        <v>0.05881060419195512</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.03137112034651823</v>
+        <v>0.02839944044870661</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.1123943011054475</v>
+        <v>0.1068744513292645</v>
       </c>
       <c r="J16" s="5" t="n">
         <v>4</v>
@@ -6372,19 +6372,19 @@
         <v>1938</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>4885</v>
+        <v>4525</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.0249555933603757</v>
+        <v>0.02395182942746693</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.006428677577263888</v>
+        <v>0.00613933637982024</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.06290800952172415</v>
+        <v>0.0559355397666669</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>15</v>
@@ -6393,19 +6393,19 @@
         <v>8179</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>4653</v>
+        <v>4675</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>13178</v>
+        <v>13718</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>0.04590384201990997</v>
+        <v>0.04373115151353041</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>0.02611836325518516</v>
+        <v>0.02499557711971042</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>0.07396538597996183</v>
+        <v>0.07334853976620417</v>
       </c>
     </row>
     <row r="17">
@@ -6422,19 +6422,19 @@
         <v>15025</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>9308</v>
+        <v>9803</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>21522</v>
+        <v>21939</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.149469486860701</v>
+        <v>0.1415847627376047</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.09260264240419167</v>
+        <v>0.09238260534760516</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.2141051635722802</v>
+        <v>0.2067430451628416</v>
       </c>
       <c r="J17" s="5" t="n">
         <v>8</v>
@@ -6443,19 +6443,19 @@
         <v>4696</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>2137</v>
+        <v>2263</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>8566</v>
+        <v>9587</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.06048112594144102</v>
+        <v>0.05804845395624493</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.02751593722881021</v>
+        <v>0.02797018627310113</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.1103213251842819</v>
+        <v>0.1185005786612274</v>
       </c>
       <c r="Q17" s="5" t="n">
         <v>28</v>
@@ -6464,19 +6464,19 @@
         <v>19721</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>14065</v>
+        <v>12759</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>28681</v>
+        <v>26993</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>0.1106870065269177</v>
+        <v>0.1054480418198612</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>0.07894166677510261</v>
+        <v>0.06822139040948993</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>0.1609776072981822</v>
+        <v>0.1443345127134826</v>
       </c>
     </row>
     <row r="18">
@@ -6487,67 +6487,67 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>22608</v>
+        <v>25797</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>15682</v>
+        <v>18448</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>30592</v>
+        <v>34882</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.224905662326861</v>
+        <v>0.2430999375354157</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.156006467656811</v>
+        <v>0.1738413927408626</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0.3043341913002089</v>
+        <v>0.3287151041980613</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>14954</v>
+        <v>16768</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>9698</v>
+        <v>11242</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>21219</v>
+        <v>22882</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.1925829289914522</v>
+        <v>0.2072626783129896</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.1248946580069655</v>
+        <v>0.1389615180275758</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.273268127113128</v>
+        <v>0.2828387646241148</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="R18" s="5" t="n">
-        <v>37561</v>
+        <v>42565</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>28533</v>
+        <v>32103</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>47650</v>
+        <v>53874</v>
       </c>
       <c r="U18" s="6" t="n">
-        <v>0.2108189238257217</v>
+        <v>0.2275972052041708</v>
       </c>
       <c r="V18" s="6" t="n">
-        <v>0.1601456434928624</v>
+        <v>0.1716532482915054</v>
       </c>
       <c r="W18" s="6" t="n">
-        <v>0.2674458048945455</v>
+        <v>0.2880666304855912</v>
       </c>
     </row>
     <row r="19">
@@ -6558,67 +6558,67 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>50333</v>
+        <v>52741</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>41683</v>
+        <v>44533</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>60357</v>
+        <v>62116</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.5007259604918324</v>
+        <v>0.4970050002562014</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>0.4146713142461109</v>
+        <v>0.4196599561901428</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.6004500250402186</v>
+        <v>0.5853543572758565</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>51641</v>
+        <v>53081</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>44959</v>
+        <v>45653</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>58322</v>
+        <v>60113</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.6650635866909056</v>
+        <v>0.6561095795394111</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.5790123116512396</v>
+        <v>0.5643006619217539</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.7511132714331791</v>
+        <v>0.7430408833381007</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="R19" s="5" t="n">
-        <v>101974</v>
+        <v>105822</v>
       </c>
       <c r="S19" s="5" t="n">
-        <v>91344</v>
+        <v>94174</v>
       </c>
       <c r="T19" s="5" t="n">
-        <v>112376</v>
+        <v>118276</v>
       </c>
       <c r="U19" s="6" t="n">
-        <v>0.5723467959620895</v>
+        <v>0.5658315723440418</v>
       </c>
       <c r="V19" s="6" t="n">
-        <v>0.5126864945208185</v>
+        <v>0.5035503212314059</v>
       </c>
       <c r="W19" s="6" t="n">
-        <v>0.6307285792009066</v>
+        <v>0.6324259736818302</v>
       </c>
     </row>
     <row r="20">
@@ -6635,19 +6635,19 @@
         <v>6314</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>3453</v>
+        <v>3016</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>12095</v>
+        <v>11459</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.06281317812549952</v>
+        <v>0.05949969527882302</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.03434901675468175</v>
+        <v>0.02842278771970382</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.1203260511084374</v>
+        <v>0.107981945112369</v>
       </c>
       <c r="J20" s="5" t="n">
         <v>7</v>
@@ -6656,19 +6656,19 @@
         <v>4419</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>1958</v>
+        <v>1776</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>8700</v>
+        <v>8429</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.05691676501582526</v>
+        <v>0.05462745876388732</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.02521111304581628</v>
+        <v>0.0219502596549084</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.1120471930632663</v>
+        <v>0.1041844287186565</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>17</v>
@@ -6677,19 +6677,19 @@
         <v>10733</v>
       </c>
       <c r="S20" s="5" t="n">
-        <v>6563</v>
+        <v>6306</v>
       </c>
       <c r="T20" s="5" t="n">
-        <v>17254</v>
+        <v>17336</v>
       </c>
       <c r="U20" s="6" t="n">
-        <v>0.06024343166536093</v>
+        <v>0.05739202911839581</v>
       </c>
       <c r="V20" s="6" t="n">
-        <v>0.03683337989018457</v>
+        <v>0.03371721694777768</v>
       </c>
       <c r="W20" s="6" t="n">
-        <v>0.09683905445775147</v>
+        <v>0.09269690150791446</v>
       </c>
     </row>
     <row r="21">
@@ -6700,16 +6700,16 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>100520</v>
+        <v>106117</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>100520</v>
+        <v>106117</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>100520</v>
+        <v>106117</v>
       </c>
       <c r="G21" s="6" t="n">
         <v>1</v>
@@ -6721,16 +6721,16 @@
         <v>1</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>77648</v>
+        <v>80902</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>77648</v>
+        <v>80902</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>77648</v>
+        <v>80902</v>
       </c>
       <c r="N21" s="6" t="n">
         <v>1</v>
@@ -6742,16 +6742,16 @@
         <v>1</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="R21" s="5" t="n">
-        <v>178168</v>
+        <v>187020</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>178168</v>
+        <v>187020</v>
       </c>
       <c r="T21" s="5" t="n">
-        <v>178168</v>
+        <v>187020</v>
       </c>
       <c r="U21" s="6" t="n">
         <v>1</v>
@@ -6781,19 +6781,19 @@
         <v>3323</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>1323</v>
+        <v>1435</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>7061</v>
+        <v>6775</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.05813269227592978</v>
+        <v>0.0560085145361388</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.02313834489524342</v>
+        <v>0.02418208886858284</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.1235294799834534</v>
+        <v>0.1142071388370707</v>
       </c>
       <c r="J22" s="5" t="n">
         <v>5</v>
@@ -6802,19 +6802,19 @@
         <v>1977</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>698</v>
+        <v>716</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>4452</v>
+        <v>4732</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.03913810043795514</v>
+        <v>0.03772330842453714</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.01381928248564745</v>
+        <v>0.01366531370654204</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.08814001635663277</v>
+        <v>0.09029573141380295</v>
       </c>
       <c r="Q22" s="5" t="n">
         <v>12</v>
@@ -6823,19 +6823,19 @@
         <v>5300</v>
       </c>
       <c r="S22" s="5" t="n">
-        <v>2784</v>
+        <v>2757</v>
       </c>
       <c r="T22" s="5" t="n">
-        <v>9305</v>
+        <v>9473</v>
       </c>
       <c r="U22" s="6" t="n">
-        <v>0.04922143014784377</v>
+        <v>0.04743190863020406</v>
       </c>
       <c r="V22" s="6" t="n">
-        <v>0.02585999716293323</v>
+        <v>0.02467797866161698</v>
       </c>
       <c r="W22" s="6" t="n">
-        <v>0.08642422951779537</v>
+        <v>0.08478268878093834</v>
       </c>
     </row>
     <row r="23">
@@ -6852,61 +6852,61 @@
         <v>5720</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>2824</v>
+        <v>2676</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>10956</v>
+        <v>10870</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.1000749344974856</v>
+        <v>0.09641818061515048</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.04941549505014104</v>
+        <v>0.0451131321357553</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.1916785739279376</v>
+        <v>0.1832288872863305</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>3545</v>
+        <v>4051</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>1589</v>
+        <v>1969</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>7340</v>
+        <v>7787</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.07017724348819961</v>
+        <v>0.0772972249080152</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.03146440578645567</v>
+        <v>0.03757349106936705</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.1453110910052743</v>
+        <v>0.1485877530701468</v>
       </c>
       <c r="Q23" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R23" s="5" t="n">
-        <v>9265</v>
+        <v>9771</v>
       </c>
       <c r="S23" s="5" t="n">
-        <v>5410</v>
+        <v>5846</v>
       </c>
       <c r="T23" s="5" t="n">
-        <v>14882</v>
+        <v>15677</v>
       </c>
       <c r="U23" s="6" t="n">
-        <v>0.08604851245689089</v>
+        <v>0.08744956956182021</v>
       </c>
       <c r="V23" s="6" t="n">
-        <v>0.05024904047006577</v>
+        <v>0.05232018756701379</v>
       </c>
       <c r="W23" s="6" t="n">
-        <v>0.1382135703642627</v>
+        <v>0.1403076010248254</v>
       </c>
     </row>
     <row r="24">
@@ -6917,67 +6917,67 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>8025</v>
+        <v>8484</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>4174</v>
+        <v>4910</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>13503</v>
+        <v>13989</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>0.1404088162992701</v>
+        <v>0.1430045391431332</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>0.07302792852365628</v>
+        <v>0.08275856857369003</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>0.2362502742957945</v>
+        <v>0.2358001324259247</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>7484</v>
+        <v>7853</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>4059</v>
+        <v>4212</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>11943</v>
+        <v>13231</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>0.1481564465577364</v>
+        <v>0.1498431712629944</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.08034947917101813</v>
+        <v>0.08037554959237421</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.236442320901598</v>
+        <v>0.2524695259696907</v>
       </c>
       <c r="Q24" s="5" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="R24" s="5" t="n">
-        <v>15509</v>
+        <v>16337</v>
       </c>
       <c r="S24" s="5" t="n">
-        <v>10186</v>
+        <v>10990</v>
       </c>
       <c r="T24" s="5" t="n">
-        <v>22639</v>
+        <v>24727</v>
       </c>
       <c r="U24" s="6" t="n">
-        <v>0.1440435963826544</v>
+        <v>0.1462121733513417</v>
       </c>
       <c r="V24" s="6" t="n">
-        <v>0.09460589510527927</v>
+        <v>0.09836001390484397</v>
       </c>
       <c r="W24" s="6" t="n">
-        <v>0.2102631324480871</v>
+        <v>0.2213066004656064</v>
       </c>
     </row>
     <row r="25">
@@ -6988,67 +6988,67 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>38409</v>
+        <v>40118</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>31750</v>
+        <v>33500</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>43839</v>
+        <v>45282</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0.6719830327464006</v>
+        <v>0.6762425413129284</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.555494225894576</v>
+        <v>0.5646800855627682</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.7669919721372536</v>
+        <v>0.7632936729874422</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>33317</v>
+        <v>34337</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>28381</v>
+        <v>28691</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>38547</v>
+        <v>39101</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.6595718710825716</v>
+        <v>0.6551787219534994</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.5618643800166149</v>
+        <v>0.5474588543008788</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.7631100367503398</v>
+        <v>0.7460837366362406</v>
       </c>
       <c r="Q25" s="5" t="n">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="R25" s="5" t="n">
-        <v>71726</v>
+        <v>74455</v>
       </c>
       <c r="S25" s="5" t="n">
-        <v>63267</v>
+        <v>65349</v>
       </c>
       <c r="T25" s="5" t="n">
-        <v>79521</v>
+        <v>81730</v>
       </c>
       <c r="U25" s="6" t="n">
-        <v>0.6661603693354754</v>
+        <v>0.666362637503422</v>
       </c>
       <c r="V25" s="6" t="n">
-        <v>0.5875963177714387</v>
+        <v>0.584863457638338</v>
       </c>
       <c r="W25" s="6" t="n">
-        <v>0.7385552140428072</v>
+        <v>0.7314792852238722</v>
       </c>
     </row>
     <row r="26">
@@ -7065,19 +7065,19 @@
         <v>1680</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>4679</v>
+        <v>4561</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.02940052418091384</v>
+        <v>0.02832622439264922</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.007773208668773268</v>
+        <v>0.007426425914297565</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.08186115000519295</v>
+        <v>0.07688307789338422</v>
       </c>
       <c r="J26" s="5" t="n">
         <v>6</v>
@@ -7086,19 +7086,19 @@
         <v>4190</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>1565</v>
+        <v>1528</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>8183</v>
+        <v>8051</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.08295633843353727</v>
+        <v>0.0799575734509539</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.03098146753115728</v>
+        <v>0.02915977389440125</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.1619967155586094</v>
+        <v>0.1536267635243004</v>
       </c>
       <c r="Q26" s="5" t="n">
         <v>9</v>
@@ -7107,19 +7107,19 @@
         <v>5871</v>
       </c>
       <c r="S26" s="5" t="n">
-        <v>2826</v>
+        <v>2803</v>
       </c>
       <c r="T26" s="5" t="n">
-        <v>11143</v>
+        <v>10452</v>
       </c>
       <c r="U26" s="6" t="n">
-        <v>0.05452609167713545</v>
+        <v>0.05254371095321202</v>
       </c>
       <c r="V26" s="6" t="n">
-        <v>0.02624513733350767</v>
+        <v>0.02508797665086356</v>
       </c>
       <c r="W26" s="6" t="n">
-        <v>0.1034878272969424</v>
+        <v>0.09354490904560939</v>
       </c>
     </row>
     <row r="27">
@@ -7130,16 +7130,16 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>57157</v>
+        <v>59325</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>57157</v>
+        <v>59325</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>57157</v>
+        <v>59325</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>1</v>
@@ -7151,16 +7151,16 @@
         <v>1</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>50513</v>
+        <v>52408</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>50513</v>
+        <v>52408</v>
       </c>
       <c r="M27" s="5" t="n">
-        <v>50513</v>
+        <v>52408</v>
       </c>
       <c r="N27" s="6" t="n">
         <v>1</v>
@@ -7172,16 +7172,16 @@
         <v>1</v>
       </c>
       <c r="Q27" s="5" t="n">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="R27" s="5" t="n">
-        <v>107671</v>
+        <v>111733</v>
       </c>
       <c r="S27" s="5" t="n">
-        <v>107671</v>
+        <v>111733</v>
       </c>
       <c r="T27" s="5" t="n">
-        <v>107671</v>
+        <v>111733</v>
       </c>
       <c r="U27" s="6" t="n">
         <v>1</v>
@@ -7211,19 +7211,19 @@
         <v>20534</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>14148</v>
+        <v>13940</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>27975</v>
+        <v>28434</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0.0703483852658234</v>
+        <v>0.06699551103094295</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>0.04846794984362418</v>
+        <v>0.04548116381266744</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>0.09583975279394617</v>
+        <v>0.0927687448251802</v>
       </c>
       <c r="J28" s="5" t="n">
         <v>17</v>
@@ -7232,19 +7232,19 @@
         <v>8585</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>4896</v>
+        <v>5068</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>13720</v>
+        <v>13440</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.03806795986969851</v>
+        <v>0.03608041215415803</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.02171094526787177</v>
+        <v>0.02129944469985413</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.06083632464368065</v>
+        <v>0.05648547856354562</v>
       </c>
       <c r="Q28" s="5" t="n">
         <v>53</v>
@@ -7253,19 +7253,19 @@
         <v>29120</v>
       </c>
       <c r="S28" s="5" t="n">
-        <v>21897</v>
+        <v>21366</v>
       </c>
       <c r="T28" s="5" t="n">
-        <v>38897</v>
+        <v>37875</v>
       </c>
       <c r="U28" s="6" t="n">
-        <v>0.05627865804347183</v>
+        <v>0.05348446176551586</v>
       </c>
       <c r="V28" s="6" t="n">
-        <v>0.04231889857449934</v>
+        <v>0.0392440478649839</v>
       </c>
       <c r="W28" s="6" t="n">
-        <v>0.07517480189291778</v>
+        <v>0.06956614436853097</v>
       </c>
     </row>
     <row r="29">
@@ -7276,67 +7276,67 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>37763</v>
+        <v>38218</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>27144</v>
+        <v>28218</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>49954</v>
+        <v>48798</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0.1293709518812234</v>
+        <v>0.1246900914331353</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>0.09299345343398234</v>
+        <v>0.09206295791293984</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>0.1711356415502998</v>
+        <v>0.1592089636104293</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>16704</v>
+        <v>18602</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>10883</v>
+        <v>13069</v>
       </c>
       <c r="M29" s="5" t="n">
-        <v>23692</v>
+        <v>25839</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.07406655022228373</v>
+        <v>0.07817702782908759</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.04825534852803748</v>
+        <v>0.05492388208840336</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.1050529577171569</v>
+        <v>0.108594308952441</v>
       </c>
       <c r="Q29" s="5" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="R29" s="5" t="n">
-        <v>54466</v>
+        <v>56820</v>
       </c>
       <c r="S29" s="5" t="n">
-        <v>43254</v>
+        <v>45272</v>
       </c>
       <c r="T29" s="5" t="n">
-        <v>67852</v>
+        <v>70234</v>
       </c>
       <c r="U29" s="6" t="n">
-        <v>0.1052660079101301</v>
+        <v>0.1043621508257013</v>
       </c>
       <c r="V29" s="6" t="n">
-        <v>0.08359662709313696</v>
+        <v>0.0831525982979171</v>
       </c>
       <c r="W29" s="6" t="n">
-        <v>0.1311358635198824</v>
+        <v>0.1290008081692676</v>
       </c>
     </row>
     <row r="30">
@@ -7347,67 +7347,67 @@
         </is>
       </c>
       <c r="C30" s="5" t="n">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>60892</v>
+        <v>66383</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>48230</v>
+        <v>53346</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>76582</v>
+        <v>80067</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.2086095731377641</v>
+        <v>0.2165797157029334</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>0.1652316491446202</v>
+        <v>0.1740473044792758</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>0.2623597931332856</v>
+        <v>0.2612252158511967</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>37945</v>
+        <v>41447</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>29094</v>
+        <v>31976</v>
       </c>
       <c r="M30" s="5" t="n">
-        <v>48073</v>
+        <v>51924</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.1682558661142347</v>
+        <v>0.1741900264775073</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.1290073165197854</v>
+        <v>0.1343863873111999</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.213164875155022</v>
+        <v>0.2182197978409949</v>
       </c>
       <c r="Q30" s="5" t="n">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="R30" s="5" t="n">
-        <v>98838</v>
+        <v>107830</v>
       </c>
       <c r="S30" s="5" t="n">
-        <v>83516</v>
+        <v>91068</v>
       </c>
       <c r="T30" s="5" t="n">
-        <v>118107</v>
+        <v>127530</v>
       </c>
       <c r="U30" s="6" t="n">
-        <v>0.1910210301348609</v>
+        <v>0.1980538432238078</v>
       </c>
       <c r="V30" s="6" t="n">
-        <v>0.1614099908667312</v>
+        <v>0.1672672462466316</v>
       </c>
       <c r="W30" s="6" t="n">
-        <v>0.2282629259288345</v>
+        <v>0.2342376885549559</v>
       </c>
     </row>
     <row r="31">
@@ -7418,67 +7418,67 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>159410</v>
+        <v>168073</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>142409</v>
+        <v>153331</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>174444</v>
+        <v>184653</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.5461204435121024</v>
+        <v>0.5483550248780469</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0.4878774869575869</v>
+        <v>0.5002576362611093</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>0.59762431096</v>
+        <v>0.6024475841741478</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>150542</v>
+        <v>157565</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>137593</v>
+        <v>146128</v>
       </c>
       <c r="M31" s="5" t="n">
-        <v>161689</v>
+        <v>169763</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.6675314183222165</v>
+        <v>0.6621933578940423</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.6101128506431798</v>
+        <v>0.6141283392862154</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.7169577939995905</v>
+        <v>0.7134569989482279</v>
       </c>
       <c r="Q31" s="5" t="n">
-        <v>443</v>
+        <v>465</v>
       </c>
       <c r="R31" s="5" t="n">
-        <v>309953</v>
+        <v>325638</v>
       </c>
       <c r="S31" s="5" t="n">
-        <v>288440</v>
+        <v>305953</v>
       </c>
       <c r="T31" s="5" t="n">
-        <v>328101</v>
+        <v>346246</v>
       </c>
       <c r="U31" s="6" t="n">
-        <v>0.5990385595659002</v>
+        <v>0.5981066149280531</v>
       </c>
       <c r="V31" s="6" t="n">
-        <v>0.5574622898505812</v>
+        <v>0.5619504617086211</v>
       </c>
       <c r="W31" s="6" t="n">
-        <v>0.63411398015484</v>
+        <v>0.6359572498400882</v>
       </c>
     </row>
     <row r="32">
@@ -7495,19 +7495,19 @@
         <v>13296</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>7850</v>
+        <v>8516</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>20486</v>
+        <v>20238</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>0.04555064620308676</v>
+        <v>0.04337965695494148</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>0.02689187425558028</v>
+        <v>0.02778399097961619</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>0.07018399340559861</v>
+        <v>0.06602743803046975</v>
       </c>
       <c r="J32" s="5" t="n">
         <v>18</v>
@@ -7516,19 +7516,19 @@
         <v>11745</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>6890</v>
+        <v>7008</v>
       </c>
       <c r="M32" s="5" t="n">
-        <v>17721</v>
+        <v>17931</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.05207820547156669</v>
+        <v>0.04935917564520475</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.03055236842057988</v>
+        <v>0.02945183780418335</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.07857911305504121</v>
+        <v>0.07535915030230152</v>
       </c>
       <c r="Q32" s="5" t="n">
         <v>38</v>
@@ -7537,19 +7537,19 @@
         <v>25041</v>
       </c>
       <c r="S32" s="5" t="n">
-        <v>17935</v>
+        <v>18254</v>
       </c>
       <c r="T32" s="5" t="n">
-        <v>34066</v>
+        <v>34405</v>
       </c>
       <c r="U32" s="6" t="n">
-        <v>0.04839574434563696</v>
+        <v>0.04599292925692193</v>
       </c>
       <c r="V32" s="6" t="n">
-        <v>0.03466298995586628</v>
+        <v>0.03352743050225886</v>
       </c>
       <c r="W32" s="6" t="n">
-        <v>0.06583932093189694</v>
+        <v>0.06319287321790572</v>
       </c>
     </row>
     <row r="33">
@@ -7560,16 +7560,16 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>404</v>
+        <v>424</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>291896</v>
+        <v>306504</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>291896</v>
+        <v>306504</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>291896</v>
+        <v>306504</v>
       </c>
       <c r="G33" s="6" t="n">
         <v>1</v>
@@ -7581,16 +7581,16 @@
         <v>1</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>342</v>
+        <v>361</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>225521</v>
+        <v>237944</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>225521</v>
+        <v>237944</v>
       </c>
       <c r="M33" s="5" t="n">
-        <v>225521</v>
+        <v>237944</v>
       </c>
       <c r="N33" s="6" t="n">
         <v>1</v>
@@ -7602,16 +7602,16 @@
         <v>1</v>
       </c>
       <c r="Q33" s="5" t="n">
-        <v>746</v>
+        <v>785</v>
       </c>
       <c r="R33" s="5" t="n">
-        <v>517417</v>
+        <v>544448</v>
       </c>
       <c r="S33" s="5" t="n">
-        <v>517417</v>
+        <v>544448</v>
       </c>
       <c r="T33" s="5" t="n">
-        <v>517417</v>
+        <v>544448</v>
       </c>
       <c r="U33" s="6" t="n">
         <v>1</v>
